--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B53465-7E0A-4FEC-923B-CFB7E848DEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C7337A-B34F-4577-A431-3BA329883278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7361" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7380" uniqueCount="1320">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -3974,6 +3974,15 @@
   </si>
   <si>
     <t>Evgeny</t>
+  </si>
+  <si>
+    <t>00:54:48.7</t>
+  </si>
+  <si>
+    <t>02:00:31.0</t>
+  </si>
+  <si>
+    <t>02:16:47.0</t>
   </si>
 </sst>
 </file>
@@ -4506,7 +4515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1291"/>
+  <dimension ref="A1:Z1294"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -36578,6 +36587,94 @@
         <v>1316</v>
       </c>
     </row>
+    <row r="1292" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1292" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B1292" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1292" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="K1292" s="1">
+        <v>46077</v>
+      </c>
+      <c r="L1292" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M1292" s="7">
+        <v>181</v>
+      </c>
+      <c r="O1292" s="7">
+        <v>12.95</v>
+      </c>
+      <c r="P1292" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Q1292" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="U1292" s="7" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1293" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1293" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1293" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1293" s="2"/>
+      <c r="E1293" s="2"/>
+      <c r="F1293" s="2"/>
+      <c r="G1293" s="2"/>
+      <c r="H1293" s="2"/>
+      <c r="I1293" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="K1293" s="1">
+        <v>46078</v>
+      </c>
+      <c r="L1293" s="4" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1294" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1294" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1294" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1294" s="2"/>
+      <c r="E1294" s="2"/>
+      <c r="F1294" s="2"/>
+      <c r="G1294" s="2"/>
+      <c r="H1294" s="2"/>
+      <c r="I1294" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K1294" s="1">
+        <v>46078</v>
+      </c>
+      <c r="L1294" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="P1294" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="Q1294" s="7" t="s">
+        <v>854</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C7337A-B34F-4577-A431-3BA329883278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACB104E-3291-45CB-923D-8C1571CABDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="all" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Z$1281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Z$1297</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7380" uniqueCount="1320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7399" uniqueCount="1321">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -3983,6 +3983,9 @@
   </si>
   <si>
     <t>02:16:47.0</t>
+  </si>
+  <si>
+    <t>01:23:50.0</t>
   </si>
 </sst>
 </file>
@@ -4515,7 +4518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1294"/>
+  <dimension ref="A1:Z1297"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -36643,6 +36646,12 @@
       <c r="L1293" s="4" t="s">
         <v>1318</v>
       </c>
+      <c r="P1293" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="Q1293" s="7" t="s">
+        <v>854</v>
+      </c>
     </row>
     <row r="1294" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1294" s="7" t="s">
@@ -36673,6 +36682,75 @@
       </c>
       <c r="Q1294" s="7" t="s">
         <v>854</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1295" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1295" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1295" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="K1295" s="1">
+        <v>46079</v>
+      </c>
+      <c r="M1295" s="7">
+        <v>3973</v>
+      </c>
+      <c r="U1295" s="7" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1296" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1296" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1296" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1296" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1296" s="1">
+        <v>46080</v>
+      </c>
+      <c r="L1296" s="7" t="s">
+        <v>1320</v>
+      </c>
+      <c r="P1296" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1296" s="7" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1297" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1297" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1297" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="I1297" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="K1297" s="1">
+        <v>46080</v>
+      </c>
+      <c r="U1297" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="V1297" s="7" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACB104E-3291-45CB-923D-8C1571CABDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECE71AF-F083-44B4-BF96-87471EE1320C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7399" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7415" uniqueCount="1323">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -3986,6 +3986,12 @@
   </si>
   <si>
     <t>01:23:50.0</t>
+  </si>
+  <si>
+    <t>02:02:34.0</t>
+  </si>
+  <si>
+    <t>02:09:49.0</t>
   </si>
 </sst>
 </file>
@@ -4518,7 +4524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1297"/>
+  <dimension ref="A1:Z1299"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -36753,6 +36759,74 @@
         <v>369</v>
       </c>
     </row>
+    <row r="1298" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1298" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1298" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1298" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1298" s="2"/>
+      <c r="E1298" s="2"/>
+      <c r="F1298" s="2"/>
+      <c r="G1298" s="2"/>
+      <c r="H1298" s="2"/>
+      <c r="I1298" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1298" s="1">
+        <v>46081</v>
+      </c>
+      <c r="L1298" s="7" t="s">
+        <v>1321</v>
+      </c>
+      <c r="P1298" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1298" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="U1298" s="7" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1299" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1299" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1299" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1299" s="2"/>
+      <c r="E1299" s="2"/>
+      <c r="F1299" s="2"/>
+      <c r="G1299" s="2"/>
+      <c r="H1299" s="2"/>
+      <c r="I1299" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1299" s="1">
+        <v>46082</v>
+      </c>
+      <c r="L1299" s="7" t="s">
+        <v>1322</v>
+      </c>
+      <c r="P1299" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1299" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="U1299" s="7" t="s">
+        <v>1061</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECE71AF-F083-44B4-BF96-87471EE1320C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5AE18E3-04A2-4BE3-B3E0-083FBB7E9ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="all" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Z$1297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Z$1301</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7415" uniqueCount="1323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7426" uniqueCount="1324">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -3992,6 +3992,9 @@
   </si>
   <si>
     <t>02:09:49.0</t>
+  </si>
+  <si>
+    <t>01:00:13.0</t>
   </si>
 </sst>
 </file>
@@ -4524,7 +4527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1299"/>
+  <dimension ref="A1:Z1301"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -35806,6 +35809,9 @@
       <c r="M1262" s="7">
         <v>470</v>
       </c>
+      <c r="N1262" s="7">
+        <v>10</v>
+      </c>
       <c r="O1262" s="7">
         <v>4.8</v>
       </c>
@@ -36031,6 +36037,9 @@
       <c r="M1271" s="7">
         <v>260</v>
       </c>
+      <c r="N1271" s="7">
+        <v>256</v>
+      </c>
       <c r="O1271" s="7">
         <v>3.99</v>
       </c>
@@ -36111,6 +36120,9 @@
       </c>
       <c r="M1274" s="7">
         <v>467</v>
+      </c>
+      <c r="N1274" s="7">
+        <v>10</v>
       </c>
       <c r="O1274" s="7">
         <v>4.21</v>
@@ -36320,6 +36332,9 @@
       <c r="M1281" s="7">
         <v>470</v>
       </c>
+      <c r="N1281" s="7">
+        <v>10</v>
+      </c>
       <c r="O1281" s="7">
         <v>4.8</v>
       </c>
@@ -36381,6 +36396,9 @@
       <c r="M1283" s="7">
         <v>513</v>
       </c>
+      <c r="N1283" s="7">
+        <v>34</v>
+      </c>
       <c r="O1283" s="7">
         <v>4.2300000000000004</v>
       </c>
@@ -36413,6 +36431,9 @@
       <c r="M1284" s="7">
         <v>445</v>
       </c>
+      <c r="N1284" s="7">
+        <v>12</v>
+      </c>
       <c r="O1284" s="7">
         <v>4.22</v>
       </c>
@@ -36536,6 +36557,9 @@
       </c>
       <c r="M1289" s="7">
         <v>470</v>
+      </c>
+      <c r="N1289" s="7">
+        <v>10</v>
       </c>
       <c r="O1289" s="7">
         <v>4.16</v>
@@ -36825,6 +36849,58 @@
       </c>
       <c r="U1299" s="7" t="s">
         <v>1061</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1300" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B1300" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1300" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="K1300" s="1">
+        <v>46083</v>
+      </c>
+      <c r="L1300" s="7" t="s">
+        <v>1323</v>
+      </c>
+      <c r="M1300" s="7">
+        <v>339</v>
+      </c>
+      <c r="O1300" s="7">
+        <v>15.3</v>
+      </c>
+      <c r="P1300" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Q1300" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="U1300" s="7" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1301" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1301" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1301" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="K1301" s="1">
+        <v>46085</v>
+      </c>
+      <c r="M1301" s="7">
+        <v>5779</v>
+      </c>
+      <c r="U1301" s="7" t="s">
+        <v>383</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5AE18E3-04A2-4BE3-B3E0-083FBB7E9ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB62A9D-E1C0-4A02-B0A9-09D81D2C6426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7426" uniqueCount="1324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7440" uniqueCount="1326">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -3995,6 +3995,12 @@
   </si>
   <si>
     <t>01:00:13.0</t>
+  </si>
+  <si>
+    <t>01:46:21.0</t>
+  </si>
+  <si>
+    <t>01:59:34.6</t>
   </si>
 </sst>
 </file>
@@ -4527,7 +4533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1301"/>
+  <dimension ref="A1:Z1303"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -36903,6 +36909,63 @@
         <v>383</v>
       </c>
     </row>
+    <row r="1302" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1302" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1302" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1302" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1302" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="K1302" s="1">
+        <v>46087</v>
+      </c>
+      <c r="L1302" s="7" t="s">
+        <v>1324</v>
+      </c>
+      <c r="P1302" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1302" s="7" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1303" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1303" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1303" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1303" s="2"/>
+      <c r="E1303" s="2"/>
+      <c r="F1303" s="2"/>
+      <c r="G1303" s="2"/>
+      <c r="H1303" s="2"/>
+      <c r="I1303" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K1303" s="1">
+        <v>46087</v>
+      </c>
+      <c r="L1303" s="7" t="s">
+        <v>1325</v>
+      </c>
+      <c r="P1303" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1303" s="7" t="s">
+        <v>854</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB62A9D-E1C0-4A02-B0A9-09D81D2C6426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9EFA16-B4A8-4773-8F71-EFBFE2DD3B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Z$1301</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7440" uniqueCount="1326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7472" uniqueCount="1330">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4001,6 +4014,18 @@
   </si>
   <si>
     <t>01:59:34.6</t>
+  </si>
+  <si>
+    <t>00:29:54.3</t>
+  </si>
+  <si>
+    <t>00:46:46.9</t>
+  </si>
+  <si>
+    <t>00:47:38.8</t>
+  </si>
+  <si>
+    <t>00:42:13.7</t>
   </si>
 </sst>
 </file>
@@ -4533,7 +4558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1303"/>
+  <dimension ref="A1:Z1309"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -36966,6 +36991,151 @@
         <v>854</v>
       </c>
     </row>
+    <row r="1304" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1304" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1304" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1304" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="K1304" s="1">
+        <v>46088</v>
+      </c>
+      <c r="M1304" s="7">
+        <f>1963+1745</f>
+        <v>3708</v>
+      </c>
+      <c r="U1304" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1305" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1305" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1305" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1305" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="K1305" s="1">
+        <v>46088</v>
+      </c>
+      <c r="L1305" s="7" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1306" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1306" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1306" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1306" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="K1306" s="1">
+        <v>46088</v>
+      </c>
+      <c r="L1306" s="7" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1307" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1307" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1307" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="K1307" s="1">
+        <v>46094</v>
+      </c>
+      <c r="M1307" s="7">
+        <v>4519</v>
+      </c>
+      <c r="U1307" s="7" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1308" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B1308" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1308" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="K1308" s="1">
+        <v>46095</v>
+      </c>
+      <c r="L1308" s="7" t="s">
+        <v>1328</v>
+      </c>
+      <c r="M1308" s="7">
+        <v>151</v>
+      </c>
+      <c r="N1308" s="7">
+        <v>10.75</v>
+      </c>
+      <c r="P1308" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Q1308" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="U1308" s="7" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1309" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B1309" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1309" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="K1309" s="1">
+        <v>46096</v>
+      </c>
+      <c r="L1309" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="M1309" s="7">
+        <v>102</v>
+      </c>
+      <c r="N1309" s="7">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="P1309" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Q1309" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="U1309" s="7" t="s">
+        <v>1061</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9EFA16-B4A8-4773-8F71-EFBFE2DD3B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86D615C-6F01-41A9-88AC-41218992BD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7472" uniqueCount="1330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7479" uniqueCount="1331">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4026,6 +4026,9 @@
   </si>
   <si>
     <t>00:42:13.7</t>
+  </si>
+  <si>
+    <t>01:26:45.0</t>
   </si>
 </sst>
 </file>
@@ -4558,7 +4561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1309"/>
+  <dimension ref="A1:Z1310"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -37136,6 +37139,32 @@
         <v>1061</v>
       </c>
     </row>
+    <row r="1310" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1310" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1310" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1310" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1310" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1310" s="1">
+        <v>46097</v>
+      </c>
+      <c r="L1310" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="P1310" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="Q1310" s="7" t="s">
+        <v>854</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86D615C-6F01-41A9-88AC-41218992BD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279A6719-220F-44B8-8BA3-A0A366F851F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
+    <workbookView xWindow="3000" yWindow="3000" windowWidth="28800" windowHeight="15410" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7479" uniqueCount="1331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7487" uniqueCount="1333">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4029,6 +4029,12 @@
   </si>
   <si>
     <t>01:26:45.0</t>
+  </si>
+  <si>
+    <t>01:39:30.0</t>
+  </si>
+  <si>
+    <t>Spuren von Breitenboden</t>
   </si>
 </sst>
 </file>
@@ -4561,7 +4567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1310"/>
+  <dimension ref="A1:Z1311"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -36794,7 +36800,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="1297" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1297" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1297" s="7" t="s">
         <v>43</v>
       </c>
@@ -36817,7 +36823,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1298" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1298" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1298" s="7" t="s">
         <v>70</v>
       </c>
@@ -36851,7 +36857,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1299" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1299" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1299" s="7" t="s">
         <v>70</v>
       </c>
@@ -36885,7 +36891,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="1300" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1300" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1300" s="7" t="s">
         <v>1082</v>
       </c>
@@ -36917,7 +36923,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="1301" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1301" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1301" s="7" t="s">
         <v>366</v>
       </c>
@@ -36937,7 +36943,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1302" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1302" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1302" s="7" t="s">
         <v>70</v>
       </c>
@@ -36963,7 +36969,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="1303" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1303" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1303" s="7" t="s">
         <v>70</v>
       </c>
@@ -36994,7 +37000,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="1304" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1304" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1304" s="7" t="s">
         <v>366</v>
       </c>
@@ -37015,7 +37021,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1305" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1305" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1305" s="7" t="s">
         <v>55</v>
       </c>
@@ -37035,7 +37041,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="1306" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1306" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1306" s="7" t="s">
         <v>55</v>
       </c>
@@ -37055,7 +37061,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="1307" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1307" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1307" s="7" t="s">
         <v>366</v>
       </c>
@@ -37075,7 +37081,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1308" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1308" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1308" s="7" t="s">
         <v>1082</v>
       </c>
@@ -37107,7 +37113,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="1309" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1309" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1309" s="7" t="s">
         <v>1082</v>
       </c>
@@ -37139,7 +37145,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="1310" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1310" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1310" s="7" t="s">
         <v>70</v>
       </c>
@@ -37163,6 +37169,40 @@
       </c>
       <c r="Q1310" s="7" t="s">
         <v>854</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1311" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1311" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1311" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1311" s="2"/>
+      <c r="E1311" s="2"/>
+      <c r="F1311" s="2"/>
+      <c r="G1311" s="2"/>
+      <c r="H1311" s="2"/>
+      <c r="I1311" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1311" s="1">
+        <v>46098</v>
+      </c>
+      <c r="L1311" s="7" t="s">
+        <v>1331</v>
+      </c>
+      <c r="P1311" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1311" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="Z1311" s="9" t="s">
+        <v>1332</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7115F571-C901-41C2-B909-E325402E1F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79147273-C5FA-4454-87B1-3A4EBDDEC3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7506" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7520" uniqueCount="1339">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4047,6 +4047,12 @@
   </si>
   <si>
     <t>00:36:49.0</t>
+  </si>
+  <si>
+    <t>00:34:39.8</t>
+  </si>
+  <si>
+    <t>01:54:29.0</t>
   </si>
 </sst>
 </file>
@@ -4579,7 +4585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1314"/>
+  <dimension ref="A1:Z1316"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -37304,6 +37310,69 @@
         <v>1053</v>
       </c>
     </row>
+    <row r="1315" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A1315" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1315" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1315" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1315" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="K1315" s="1">
+        <v>46104</v>
+      </c>
+      <c r="L1315" s="7" t="s">
+        <v>1337</v>
+      </c>
+      <c r="N1315" s="7">
+        <v>42</v>
+      </c>
+      <c r="O1315" s="7">
+        <v>3.87</v>
+      </c>
+      <c r="Q1315" s="7" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A1316" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1316" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1316" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1316" s="2"/>
+      <c r="E1316" s="2"/>
+      <c r="F1316" s="2"/>
+      <c r="G1316" s="2"/>
+      <c r="H1316" s="2"/>
+      <c r="I1316" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1316" s="1">
+        <v>46105</v>
+      </c>
+      <c r="L1316" s="7" t="s">
+        <v>1338</v>
+      </c>
+      <c r="P1316" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1316" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="U1316" s="7" t="s">
+        <v>383</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79147273-C5FA-4454-87B1-3A4EBDDEC3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E02CB73-45C8-41EF-8BB7-E26888086E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7520" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7525" uniqueCount="1339">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4585,7 +4585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1316"/>
+  <dimension ref="A1:Z1317"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -37341,35 +37341,64 @@
     </row>
     <row r="1316" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1316" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1316" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1316" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="I1316" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="K1316" s="1">
+        <v>46104</v>
+      </c>
+      <c r="M1316" s="7">
+        <v>496</v>
+      </c>
+      <c r="N1316" s="7">
+        <v>42</v>
+      </c>
+      <c r="O1316" s="7">
+        <v>3.87</v>
+      </c>
+      <c r="Q1316" s="7" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A1317" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B1316" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1316" s="2" t="s">
+      <c r="B1317" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1317" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D1316" s="2"/>
-      <c r="E1316" s="2"/>
-      <c r="F1316" s="2"/>
-      <c r="G1316" s="2"/>
-      <c r="H1316" s="2"/>
-      <c r="I1316" s="2" t="s">
+      <c r="D1317" s="2"/>
+      <c r="E1317" s="2"/>
+      <c r="F1317" s="2"/>
+      <c r="G1317" s="2"/>
+      <c r="H1317" s="2"/>
+      <c r="I1317" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="K1316" s="1">
+      <c r="K1317" s="1">
         <v>46105</v>
       </c>
-      <c r="L1316" s="7" t="s">
+      <c r="L1317" s="7" t="s">
         <v>1338</v>
       </c>
-      <c r="P1316" s="7" t="s">
+      <c r="P1317" s="7" t="s">
         <v>671</v>
       </c>
-      <c r="Q1316" s="7" t="s">
+      <c r="Q1317" s="7" t="s">
         <v>854</v>
       </c>
-      <c r="U1316" s="7" t="s">
+      <c r="U1317" s="7" t="s">
         <v>383</v>
       </c>
     </row>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46345520-606B-4610-807A-2B8627E07484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0291F4-CCBF-4370-BD42-637FDC7B62EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7549" uniqueCount="1343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7556" uniqueCount="1344">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4065,6 +4065,9 @@
   </si>
   <si>
     <t>01:31:45.0</t>
+  </si>
+  <si>
+    <t>01:39:44.4</t>
   </si>
 </sst>
 </file>
@@ -4597,7 +4600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1321"/>
+  <dimension ref="A1:Z1322"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -37536,6 +37539,32 @@
         <v>854</v>
       </c>
     </row>
+    <row r="1322" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1322" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1322" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1322" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="I1322" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="K1322" s="1">
+        <v>46115</v>
+      </c>
+      <c r="L1322" s="7" t="s">
+        <v>1343</v>
+      </c>
+      <c r="P1322" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="Q1322" s="7" t="s">
+        <v>854</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC7E633-5B2D-4209-88F3-39F3482FE75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66A2AC3-2E2D-4726-8999-53726DA8BDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7587" uniqueCount="1346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7595" uniqueCount="1347">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4074,6 +4074,9 @@
   </si>
   <si>
     <t>01:36:22.0</t>
+  </si>
+  <si>
+    <t>03:09:41.0</t>
   </si>
 </sst>
 </file>
@@ -4606,7 +4609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1326"/>
+  <dimension ref="A1:Z1327"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -37684,6 +37687,35 @@
         <v>854</v>
       </c>
     </row>
+    <row r="1327" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1327" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1327" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1327" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1327" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1327" s="1">
+        <v>46130</v>
+      </c>
+      <c r="L1327" s="7" t="s">
+        <v>1346</v>
+      </c>
+      <c r="P1327" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1327" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="U1327" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA075BE5-CB03-4A01-B669-285F79BBFEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FFEAE8-0E58-4D3C-B5BB-1394186F069A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="all" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Z$1330</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Z$1333</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7617" uniqueCount="1351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7644" uniqueCount="1356">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4089,6 +4089,21 @@
   </si>
   <si>
     <t>02:27:50.0</t>
+  </si>
+  <si>
+    <t>02:02:33.0</t>
+  </si>
+  <si>
+    <t>Obertaljoch</t>
+  </si>
+  <si>
+    <t>01:16:21.0</t>
+  </si>
+  <si>
+    <t>Sustenderby</t>
+  </si>
+  <si>
+    <t>Obertal Pt 2717</t>
   </si>
 </sst>
 </file>
@@ -4621,7 +4636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1330"/>
+  <dimension ref="A1:Z1333"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -34901,7 +34916,7 @@
         <v>813</v>
       </c>
       <c r="M1226" s="7">
-        <v>1217</v>
+        <v>1191</v>
       </c>
       <c r="P1226" s="7" t="s">
         <v>816</v>
@@ -34939,7 +34954,7 @@
         <v>387</v>
       </c>
       <c r="M1227" s="7">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="P1227" s="7" t="s">
         <v>816</v>
@@ -34971,7 +34986,7 @@
         <v>1263</v>
       </c>
       <c r="M1228" s="7">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="P1228" s="7" t="s">
         <v>671</v>
@@ -35006,7 +35021,7 @@
         <v>1264</v>
       </c>
       <c r="M1229" s="7">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="P1229" s="7" t="s">
         <v>671</v>
@@ -35103,6 +35118,9 @@
       <c r="L1232" s="7" t="s">
         <v>1265</v>
       </c>
+      <c r="M1232" s="7">
+        <v>942</v>
+      </c>
       <c r="P1232" s="7" t="s">
         <v>816</v>
       </c>
@@ -35224,6 +35242,9 @@
       <c r="L1236" s="7" t="s">
         <v>1268</v>
       </c>
+      <c r="M1236" s="7">
+        <v>939</v>
+      </c>
       <c r="P1236" s="7" t="s">
         <v>816</v>
       </c>
@@ -36376,7 +36397,7 @@
         <v>1303</v>
       </c>
       <c r="M1278" s="7">
-        <v>1464</v>
+        <v>1447</v>
       </c>
       <c r="P1278" s="7" t="s">
         <v>671</v>
@@ -36408,7 +36429,7 @@
         <v>1304</v>
       </c>
       <c r="M1279" s="7">
-        <v>1689</v>
+        <v>1662</v>
       </c>
       <c r="P1279" s="7" t="s">
         <v>671</v>
@@ -36809,6 +36830,9 @@
       <c r="L1293" s="4" t="s">
         <v>1317</v>
       </c>
+      <c r="M1293" s="7">
+        <v>1261</v>
+      </c>
       <c r="P1293" s="7" t="s">
         <v>816</v>
       </c>
@@ -36841,7 +36865,7 @@
         <v>1318</v>
       </c>
       <c r="M1294" s="7">
-        <v>1442</v>
+        <v>1428</v>
       </c>
       <c r="P1294" s="7" t="s">
         <v>816</v>
@@ -36890,7 +36914,7 @@
         <v>1319</v>
       </c>
       <c r="M1296" s="7">
-        <v>950</v>
+        <v>928</v>
       </c>
       <c r="P1296" s="7" t="s">
         <v>671</v>
@@ -36947,7 +36971,7 @@
         <v>1320</v>
       </c>
       <c r="M1298" s="7">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="P1298" s="7" t="s">
         <v>671</v>
@@ -37067,6 +37091,9 @@
       <c r="L1302" s="7" t="s">
         <v>1323</v>
       </c>
+      <c r="M1302" s="7">
+        <v>1274</v>
+      </c>
       <c r="P1302" s="7" t="s">
         <v>671</v>
       </c>
@@ -37099,7 +37126,7 @@
         <v>1324</v>
       </c>
       <c r="M1303" s="7">
-        <v>1459</v>
+        <v>1444</v>
       </c>
       <c r="P1303" s="7" t="s">
         <v>671</v>
@@ -37495,7 +37522,7 @@
         <v>1337</v>
       </c>
       <c r="M1317" s="7">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="P1317" s="7" t="s">
         <v>671</v>
@@ -37648,9 +37675,6 @@
       <c r="L1322" s="7" t="s">
         <v>1342</v>
       </c>
-      <c r="M1322" s="7">
-        <v>1158</v>
-      </c>
       <c r="P1322" s="7" t="s">
         <v>816</v>
       </c>
@@ -37717,9 +37741,6 @@
       <c r="L1325" s="7" t="s">
         <v>1343</v>
       </c>
-      <c r="M1325" s="7">
-        <v>1675</v>
-      </c>
       <c r="P1325" s="7" t="s">
         <v>816</v>
       </c>
@@ -37747,7 +37768,7 @@
         <v>1345</v>
       </c>
       <c r="M1326" s="7">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="P1326" s="7" t="s">
         <v>816</v>
@@ -37776,7 +37797,7 @@
         <v>1346</v>
       </c>
       <c r="M1327" s="7">
-        <v>1676</v>
+        <v>1659</v>
       </c>
       <c r="P1327" s="7" t="s">
         <v>671</v>
@@ -37823,7 +37844,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="1329" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1329" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1329" s="7" t="s">
         <v>70</v>
       </c>
@@ -37843,7 +37864,7 @@
         <v>1347</v>
       </c>
       <c r="M1329" s="7">
-        <v>987</v>
+        <v>965</v>
       </c>
       <c r="P1329" s="7" t="s">
         <v>671</v>
@@ -37855,7 +37876,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1330" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1330" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1330" s="7" t="s">
         <v>70</v>
       </c>
@@ -37875,13 +37896,115 @@
         <v>1350</v>
       </c>
       <c r="M1330" s="7">
-        <v>1475</v>
+        <v>1463</v>
       </c>
       <c r="P1330" s="7" t="s">
         <v>671</v>
       </c>
       <c r="Q1330" s="7" t="s">
         <v>854</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1331" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1331" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1331" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1331" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="K1331" s="1">
+        <v>46136</v>
+      </c>
+      <c r="L1331" s="7" t="s">
+        <v>1351</v>
+      </c>
+      <c r="M1331" s="7">
+        <v>952</v>
+      </c>
+      <c r="P1331" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1331" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="U1331" s="7" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1332" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1332" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1332" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1332" t="s">
+        <v>1355</v>
+      </c>
+      <c r="K1332" s="1">
+        <v>46167</v>
+      </c>
+      <c r="L1332" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1332" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="Q1332" s="7" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1333" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1333" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1333" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1333" s="9" t="s">
+        <v>1352</v>
+      </c>
+      <c r="K1333" s="1">
+        <v>46167</v>
+      </c>
+      <c r="L1333" s="7" t="s">
+        <v>1353</v>
+      </c>
+      <c r="M1333" s="7">
+        <v>1074</v>
+      </c>
+      <c r="P1333" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="Q1333" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="U1333" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="V1333" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="W1333" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="X1333" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="Z1333" s="9" t="s">
+        <v>1354</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FFEAE8-0E58-4D3C-B5BB-1394186F069A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8E26B4-4474-4738-B1D9-A588B758E6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7644" uniqueCount="1356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7661" uniqueCount="1357">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4104,6 +4104,9 @@
   </si>
   <si>
     <t>Obertal Pt 2717</t>
+  </si>
+  <si>
+    <t>03:29:04.0</t>
   </si>
 </sst>
 </file>
@@ -4636,7 +4639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1333"/>
+  <dimension ref="A1:Z1335"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -37951,7 +37954,7 @@
         <v>1355</v>
       </c>
       <c r="K1332" s="1">
-        <v>46167</v>
+        <v>46137</v>
       </c>
       <c r="L1332" s="7" t="s">
         <v>59</v>
@@ -37977,7 +37980,7 @@
         <v>1352</v>
       </c>
       <c r="K1333" s="1">
-        <v>46167</v>
+        <v>46137</v>
       </c>
       <c r="L1333" s="7" t="s">
         <v>1353</v>
@@ -38005,6 +38008,73 @@
       </c>
       <c r="Z1333" s="9" t="s">
         <v>1354</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1334" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1334" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1334" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="D1334" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="E1334" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="F1334" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="G1334" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="I1334" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="J1334" s="7">
+        <v>1</v>
+      </c>
+      <c r="K1334" s="1">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1335" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1335" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1335" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1335" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="K1335" s="1">
+        <v>46139</v>
+      </c>
+      <c r="L1335" s="7" t="s">
+        <v>1356</v>
+      </c>
+      <c r="M1335" s="7">
+        <v>1553</v>
+      </c>
+      <c r="P1335" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1335" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="U1335" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="V1335" s="7" t="s">
+        <v>811</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8E26B4-4474-4738-B1D9-A588B758E6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FA311F-01BF-4F2E-924F-8A12F04D917E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Z$1333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Z$1335</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7661" uniqueCount="1357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7669" uniqueCount="1358">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4107,6 +4107,9 @@
   </si>
   <si>
     <t>03:29:04.0</t>
+  </si>
+  <si>
+    <t>03:22:05.0</t>
   </si>
 </sst>
 </file>
@@ -4639,7 +4642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1335"/>
+  <dimension ref="A1:Z1336"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -38077,6 +38080,38 @@
         <v>811</v>
       </c>
     </row>
+    <row r="1336" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1336" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1336" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1336" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1336" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1336" s="1">
+        <v>46143</v>
+      </c>
+      <c r="L1336" s="7" t="s">
+        <v>1357</v>
+      </c>
+      <c r="M1336" s="7">
+        <v>1656</v>
+      </c>
+      <c r="P1336" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q1336" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="U1336" s="7" t="s">
+        <v>842</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028A0436-6AE7-4D87-BA0E-E3CCFCC35833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D1A766-DDD1-4BFA-839E-0398A9EDE167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7689" uniqueCount="1361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7711" uniqueCount="1366">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4119,6 +4119,21 @@
   </si>
   <si>
     <t>00:55:03.7</t>
+  </si>
+  <si>
+    <t>Brienzwiler</t>
+  </si>
+  <si>
+    <t>01:10:58.0</t>
+  </si>
+  <si>
+    <t>01:03:06.0</t>
+  </si>
+  <si>
+    <t>02:57:48.0</t>
+  </si>
+  <si>
+    <t>Anstehen bei der Steilstufe...</t>
   </si>
 </sst>
 </file>
@@ -4651,7 +4666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1340"/>
+  <dimension ref="A1:Z1343"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -38219,6 +38234,108 @@
         <v>1360</v>
       </c>
     </row>
+    <row r="1341" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1341" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1341" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1341" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="I1341" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="K1341" s="1">
+        <v>46156</v>
+      </c>
+      <c r="L1341" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="M1341" s="7">
+        <v>556</v>
+      </c>
+      <c r="N1341" s="7">
+        <v>151</v>
+      </c>
+      <c r="O1341" s="7">
+        <v>7.8</v>
+      </c>
+      <c r="Q1341" s="7" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1342" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1342" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1342" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="D1342" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="E1342" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="I1342" s="9" t="s">
+        <v>1361</v>
+      </c>
+      <c r="K1342" s="1">
+        <v>46158</v>
+      </c>
+      <c r="L1342" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="M1342" s="7">
+        <v>244</v>
+      </c>
+      <c r="N1342" s="7">
+        <v>270</v>
+      </c>
+      <c r="O1342" s="7">
+        <v>11.44</v>
+      </c>
+      <c r="Q1342" s="7" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1343" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1343" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1343" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="I1343" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1343" s="1">
+        <v>46159</v>
+      </c>
+      <c r="L1343" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="M1343" s="7">
+        <v>1574</v>
+      </c>
+      <c r="P1343" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q1343" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="Z1343" s="9" t="s">
+        <v>1365</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D0D556-3689-403E-9575-19359CB3054F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2442AEB4-40DB-4533-82E2-45C8119696CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7739" uniqueCount="1370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7755" uniqueCount="1373">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4146,6 +4146,15 @@
   </si>
   <si>
     <t>02:41:43.0</t>
+  </si>
+  <si>
+    <t>00:41:23.1</t>
+  </si>
+  <si>
+    <t>00:31:53.3</t>
+  </si>
+  <si>
+    <t>00:59:51.6</t>
   </si>
 </sst>
 </file>
@@ -4678,7 +4687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1348"/>
+  <dimension ref="A1:Z1351"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -38383,7 +38392,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="1345" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1345" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1345" s="7" t="s">
         <v>55</v>
       </c>
@@ -38403,7 +38412,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="1346" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1346" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1346" s="7" t="s">
         <v>55</v>
       </c>
@@ -38423,7 +38432,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="1347" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1347" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1347" s="7" t="s">
         <v>55</v>
       </c>
@@ -38443,7 +38452,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="1348" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1348" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1348" s="7" t="s">
         <v>70</v>
       </c>
@@ -38470,6 +38479,78 @@
       </c>
       <c r="Q1348" s="7" t="s">
         <v>853</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1349" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1349" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C1349" s="9" t="s">
+        <v>1059</v>
+      </c>
+      <c r="K1349" s="1">
+        <v>46169</v>
+      </c>
+      <c r="L1349" s="7" t="s">
+        <v>1370</v>
+      </c>
+      <c r="M1349" s="7">
+        <v>89</v>
+      </c>
+      <c r="N1349" s="7">
+        <v>89</v>
+      </c>
+      <c r="O1349" s="7">
+        <v>7.1</v>
+      </c>
+      <c r="Q1349" s="7" t="s">
+        <v>950</v>
+      </c>
+      <c r="U1349" s="7" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1350" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1350" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1350" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1350" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="K1350" s="1">
+        <v>46170</v>
+      </c>
+      <c r="L1350" s="7" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1351" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1351" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1351" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1351" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="K1351" s="1">
+        <v>46170</v>
+      </c>
+      <c r="L1351" s="7" t="s">
+        <v>1372</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2442AEB4-40DB-4533-82E2-45C8119696CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF08CA50-2B3A-486D-8890-E7E582BB19E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -4154,7 +4154,7 @@
     <t>00:31:53.3</t>
   </si>
   <si>
-    <t>00:59:51.6</t>
+    <t>00:49:51.6</t>
   </si>
 </sst>
 </file>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1C9F17-9764-4006-B641-B40AF9D88483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB50FE5-DFAF-491B-8E16-5F05C5AB1525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7788" uniqueCount="1378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7797" uniqueCount="1379">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4170,6 +4170,9 @@
   </si>
   <si>
     <t>00:33:48.4</t>
+  </si>
+  <si>
+    <t>00:52:51.6</t>
   </si>
 </sst>
 </file>
@@ -4702,7 +4705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1355"/>
+  <dimension ref="A1:Z1356"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -38646,6 +38649,9 @@
       <c r="O1353" s="7">
         <v>7.2</v>
       </c>
+      <c r="Q1353" s="7" t="s">
+        <v>950</v>
+      </c>
       <c r="U1353" s="7" t="s">
         <v>1060</v>
       </c>
@@ -38675,6 +38681,9 @@
       <c r="O1354" s="7">
         <v>6.53</v>
       </c>
+      <c r="Q1354" s="7" t="s">
+        <v>950</v>
+      </c>
       <c r="U1354" s="7" t="s">
         <v>1060</v>
       </c>
@@ -38700,6 +38709,41 @@
       </c>
       <c r="L1355" s="7" t="s">
         <v>1375</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1356" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1356" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1356" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="D1356" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="I1356" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="K1356" s="1">
+        <v>46179</v>
+      </c>
+      <c r="L1356" s="7" t="s">
+        <v>1378</v>
+      </c>
+      <c r="M1356" s="7">
+        <v>521</v>
+      </c>
+      <c r="N1356" s="7">
+        <v>72</v>
+      </c>
+      <c r="O1356" s="7">
+        <v>7.6</v>
+      </c>
+      <c r="Q1356" s="7" t="s">
+        <v>1052</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB50FE5-DFAF-491B-8E16-5F05C5AB1525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A4746C-AB80-4E35-9C12-4C39CBD7DD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7797" uniqueCount="1379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7807" uniqueCount="1381">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4173,6 +4173,12 @@
   </si>
   <si>
     <t>00:52:51.6</t>
+  </si>
+  <si>
+    <t>00:24:37.1</t>
+  </si>
+  <si>
+    <t>01:18:12.0</t>
   </si>
 </sst>
 </file>
@@ -4705,7 +4711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1356"/>
+  <dimension ref="A1:Z1358"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -38746,6 +38752,46 @@
         <v>1052</v>
       </c>
     </row>
+    <row r="1357" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1357" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1357" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1357" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1357" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1357" s="1">
+        <v>46181</v>
+      </c>
+      <c r="L1357" s="7" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1358" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1358" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1358" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1358" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="K1358" s="1">
+        <v>46181</v>
+      </c>
+      <c r="L1358" s="7" t="s">
+        <v>1380</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1035">
     <sortCondition ref="K2:K1035"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAE1E5E-B2E4-4E95-B98F-7DB2455B3259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA338D6E-5590-4C6B-9C9E-F437A0CD3060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7858" uniqueCount="1391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7900" uniqueCount="1397">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4209,6 +4209,24 @@
   </si>
   <si>
     <t>01:52:53.9</t>
+  </si>
+  <si>
+    <t>00:40:58.1</t>
+  </si>
+  <si>
+    <t>00:31:48.5</t>
+  </si>
+  <si>
+    <t>00:48:25.7</t>
+  </si>
+  <si>
+    <t>00:30:32.1</t>
+  </si>
+  <si>
+    <t>00:56:31.2</t>
+  </si>
+  <si>
+    <t>01:18:53.0</t>
   </si>
 </sst>
 </file>
@@ -4741,7 +4759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1367"/>
+  <dimension ref="A1:Z1375"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -38862,178 +38880,379 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="1361" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1361" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1361" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B1361" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1361" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="D1361" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="I1361" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="J1361" s="7">
+        <v>1</v>
+      </c>
+      <c r="K1361" s="1">
+        <v>46182</v>
+      </c>
+      <c r="L1361" s="7" t="s">
+        <v>1391</v>
+      </c>
+      <c r="M1361" s="7">
+        <v>161</v>
+      </c>
+      <c r="N1361" s="7">
+        <v>154</v>
+      </c>
+      <c r="O1361" s="7">
+        <v>6.57</v>
+      </c>
+      <c r="Q1361" s="7" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1362" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1362" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1362" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1362" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="K1362" s="1">
+        <v>46184</v>
+      </c>
+      <c r="L1362" s="7" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1363" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1363" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1363" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1363" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="K1363" s="1">
+        <v>46184</v>
+      </c>
+      <c r="L1363" s="7" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1364" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1364" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1364" s="9" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K1364" s="1">
+        <v>46185</v>
+      </c>
+      <c r="M1364" s="7">
+        <v>3.77</v>
+      </c>
+      <c r="N1364" s="7">
+        <v>16</v>
+      </c>
+      <c r="O1364" s="7">
+        <v>16</v>
+      </c>
+      <c r="Q1364" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="U1364" s="7" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1365" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1365" s="7" t="s">
         <v>779</v>
       </c>
-      <c r="C1361" s="9" t="s">
+      <c r="C1365" s="9" t="s">
         <v>1150</v>
       </c>
-      <c r="I1361" s="9" t="s">
+      <c r="I1365" s="9" t="s">
         <v>1382</v>
       </c>
-      <c r="K1361" s="1">
+      <c r="K1365" s="1">
         <v>46186</v>
       </c>
-      <c r="L1361" s="6" t="s">
+      <c r="L1365" s="6" t="s">
         <v>1383</v>
       </c>
     </row>
-    <row r="1362" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1362" s="7" t="s">
+    <row r="1366" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1366" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B1362" s="7" t="s">
+      <c r="B1366" s="7" t="s">
         <v>779</v>
       </c>
-      <c r="C1362" s="9" t="s">
+      <c r="C1366" s="9" t="s">
         <v>1382</v>
       </c>
-      <c r="I1362" s="9" t="s">
+      <c r="I1366" s="9" t="s">
         <v>1151</v>
       </c>
-      <c r="K1362" s="1">
+      <c r="K1366" s="1">
         <v>46186</v>
       </c>
-      <c r="L1362" s="6" t="s">
+      <c r="L1366" s="6" t="s">
         <v>1384</v>
       </c>
     </row>
-    <row r="1363" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1363" s="7" t="s">
+    <row r="1367" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1367" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B1363" s="7" t="s">
+      <c r="B1367" s="7" t="s">
         <v>779</v>
       </c>
-      <c r="C1363" s="9" t="s">
+      <c r="C1367" s="9" t="s">
         <v>1150</v>
       </c>
-      <c r="I1363" s="9" t="s">
+      <c r="I1367" s="9" t="s">
         <v>1151</v>
       </c>
-      <c r="K1363" s="1">
+      <c r="K1367" s="1">
         <v>46186</v>
       </c>
-      <c r="L1363" s="7" t="s">
+      <c r="L1367" s="7" t="s">
         <v>1381</v>
       </c>
-      <c r="M1363" s="7">
+      <c r="M1367" s="7">
         <v>892</v>
       </c>
-      <c r="N1363" s="7">
+      <c r="N1367" s="7">
         <v>63</v>
       </c>
-      <c r="O1363" s="7">
+      <c r="O1367" s="7">
         <v>8.5500000000000007</v>
       </c>
-      <c r="Q1363" s="7" t="s">
+      <c r="Q1367" s="7" t="s">
         <v>1052</v>
       </c>
     </row>
-    <row r="1364" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1364" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1364" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1364" s="2" t="s">
+    <row r="1368" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1368" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1368" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1368" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I1364" s="9" t="s">
+      <c r="I1368" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="K1364" s="1">
+      <c r="K1368" s="1">
         <v>46190</v>
       </c>
-      <c r="L1364" s="7" t="s">
+      <c r="L1368" s="7" t="s">
         <v>1388</v>
       </c>
     </row>
-    <row r="1365" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1365" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1365" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1365" s="2" t="s">
+    <row r="1369" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1369" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1369" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1369" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I1365" s="2" t="s">
+      <c r="I1369" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="K1365" s="1">
+      <c r="K1369" s="1">
         <v>46190</v>
       </c>
-      <c r="L1365" s="7" t="s">
+      <c r="L1369" s="7" t="s">
         <v>1389</v>
       </c>
     </row>
-    <row r="1366" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1366" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1366" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1366" s="2" t="s">
+    <row r="1370" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1370" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1370" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1370" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D1366" s="2" t="s">
+      <c r="D1370" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E1366" s="2" t="s">
+      <c r="E1370" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="F1366" s="2"/>
-      <c r="G1366" s="2"/>
-      <c r="H1366" s="2"/>
-      <c r="I1366" s="2" t="s">
+      <c r="F1370" s="2"/>
+      <c r="G1370" s="2"/>
+      <c r="H1370" s="2"/>
+      <c r="I1370" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="K1366" s="1">
+      <c r="K1370" s="1">
         <v>46190</v>
       </c>
-      <c r="L1366" s="7" t="s">
+      <c r="L1370" s="7" t="s">
         <v>1390</v>
       </c>
     </row>
-    <row r="1367" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1367" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1367" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1367" s="2" t="s">
+    <row r="1371" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1371" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1371" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1371" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D1367" s="2" t="s">
+      <c r="D1371" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E1367" s="2" t="s">
+      <c r="E1371" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="F1367" s="2" t="s">
+      <c r="F1371" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="G1367" s="2" t="s">
+      <c r="G1371" s="2" t="s">
         <v>1387</v>
       </c>
-      <c r="H1367" s="2"/>
-      <c r="I1367" s="2" t="s">
+      <c r="H1371" s="2"/>
+      <c r="I1371" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J1367" s="7">
+      <c r="J1371" s="7">
         <v>1</v>
       </c>
-      <c r="K1367" s="1">
+      <c r="K1371" s="1">
         <v>46190</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1372" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1372" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1372" s="9" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K1372" s="1">
+        <v>46192</v>
+      </c>
+      <c r="M1372" s="7">
+        <v>25</v>
+      </c>
+      <c r="N1372" s="7">
+        <v>26</v>
+      </c>
+      <c r="O1372" s="7">
+        <v>2.34</v>
+      </c>
+      <c r="Q1372" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="U1372" s="7" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1373" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1373" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1373" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1373" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="K1373" s="1">
+        <v>46192</v>
+      </c>
+      <c r="L1373" s="7" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1374" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1374" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1374" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1374" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="K1374" s="1">
+        <v>46192</v>
+      </c>
+      <c r="L1374" s="7" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1375" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1375" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1375" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1375" s="2"/>
+      <c r="E1375" s="2"/>
+      <c r="F1375" s="2"/>
+      <c r="G1375" s="2"/>
+      <c r="H1375" s="2"/>
+      <c r="I1375" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="K1375" s="1">
+        <v>46192</v>
+      </c>
+      <c r="L1375" s="7" t="s">
+        <v>1396</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39505D58-98A5-41EE-BB80-4A27956B53AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1C9C69-1CC4-4A41-B7A5-4A47D5FCD9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Z$1383</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7967" uniqueCount="1407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7982" uniqueCount="1408">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4257,6 +4257,9 @@
   </si>
   <si>
     <t>Bonistock</t>
+  </si>
+  <si>
+    <t>01:11:45.0</t>
   </si>
 </sst>
 </file>
@@ -4789,7 +4792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1388"/>
+  <dimension ref="A1:Z1391"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.26953125" style="7" bestFit="1" customWidth="1"/>
@@ -39640,6 +39643,85 @@
         <v>46206</v>
       </c>
     </row>
+    <row r="1389" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1389" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1389" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1389" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="I1389" s="9" t="s">
+        <v>1359</v>
+      </c>
+      <c r="K1389" s="1">
+        <v>46208</v>
+      </c>
+      <c r="M1389" s="7">
+        <v>222</v>
+      </c>
+      <c r="N1389" s="7">
+        <v>242</v>
+      </c>
+      <c r="O1389" s="7">
+        <v>10.33</v>
+      </c>
+      <c r="Q1389" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="U1389" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1390" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1390" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1390" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1390" s="2"/>
+      <c r="E1390" s="2"/>
+      <c r="F1390" s="2"/>
+      <c r="G1390" s="2"/>
+      <c r="H1390" s="2"/>
+      <c r="I1390" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="K1390" s="1">
+        <v>46209</v>
+      </c>
+      <c r="L1390" s="7" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1391" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1391" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1391" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1391" s="2"/>
+      <c r="E1391" s="2"/>
+      <c r="F1391" s="2"/>
+      <c r="G1391" s="2"/>
+      <c r="H1391" s="2"/>
+      <c r="I1391" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K1391" s="1">
+        <v>46209</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z1383">
     <sortCondition ref="K2:K1383"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBA99B7-18AE-45BB-B80B-C265878A8158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E8C852-1E0E-4852-BACF-C962ABFF33A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8165" uniqueCount="1445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8209" uniqueCount="1452">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4371,6 +4371,27 @@
   </si>
   <si>
     <t>01:02:59.0</t>
+  </si>
+  <si>
+    <t>00:27:53.2</t>
+  </si>
+  <si>
+    <t>00:53:35.5</t>
+  </si>
+  <si>
+    <t>00:55:34.1</t>
+  </si>
+  <si>
+    <t>Tannalp</t>
+  </si>
+  <si>
+    <t>Sarnen</t>
+  </si>
+  <si>
+    <t>00:27:45.9</t>
+  </si>
+  <si>
+    <t>00:55:08.1</t>
   </si>
 </sst>
 </file>
@@ -4412,7 +4433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4454,19 +4475,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4919,7 +4927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Z1433"/>
+  <dimension ref="A1:Z1440"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.6328125" style="7" customWidth="1"/>
@@ -4933,7 +4941,7 @@
     <col min="9" max="9" width="22.453125" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.54296875" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.453125" style="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.54296875" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.26953125" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.54296875" style="7" bestFit="1" customWidth="1"/>
@@ -40530,7 +40538,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="1425" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1425" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1425" s="7" t="s">
         <v>55</v>
       </c>
@@ -40552,7 +40560,7 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="1426" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1426" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1426" s="7" t="s">
         <v>1432</v>
       </c>
@@ -40575,7 +40583,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1427" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1427" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1427" s="7" t="s">
         <v>51</v>
       </c>
@@ -40607,7 +40615,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1428" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1428" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1428" s="7" t="s">
         <v>1432</v>
       </c>
@@ -40630,7 +40638,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1429" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1429" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1429" s="7" t="s">
         <v>55</v>
       </c>
@@ -40650,7 +40658,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="1430" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1430" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1430" s="7" t="s">
         <v>55</v>
       </c>
@@ -40670,82 +40678,301 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="1431" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1431" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1431" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1431" s="15" t="s">
+    <row r="1431" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1431" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1431" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1431" t="s">
         <v>1436</v>
       </c>
-      <c r="D1431" s="17"/>
-      <c r="E1431" s="17"/>
-      <c r="F1431" s="17"/>
-      <c r="G1431" s="17"/>
-      <c r="H1431" s="17"/>
-      <c r="I1431" s="17" t="s">
+      <c r="D1431" s="2"/>
+      <c r="E1431" s="2"/>
+      <c r="F1431" s="2"/>
+      <c r="G1431" s="2"/>
+      <c r="H1431" s="2"/>
+      <c r="I1431" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="J1431" s="18"/>
-      <c r="K1431" s="16">
+      <c r="K1431" s="1">
         <v>46215</v>
       </c>
       <c r="L1431" s="7" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="1432" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1432" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1432" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1432" s="15" t="s">
+    <row r="1432" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1432" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1432" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1432" t="s">
         <v>1436</v>
       </c>
-      <c r="D1432" s="17"/>
-      <c r="E1432" s="17"/>
-      <c r="F1432" s="17"/>
-      <c r="G1432" s="17"/>
-      <c r="H1432" s="17"/>
-      <c r="I1432" s="17" t="s">
+      <c r="D1432" s="2"/>
+      <c r="E1432" s="2"/>
+      <c r="F1432" s="2"/>
+      <c r="G1432" s="2"/>
+      <c r="H1432" s="2"/>
+      <c r="I1432" s="2" t="s">
         <v>1435</v>
       </c>
-      <c r="J1432" s="18"/>
-      <c r="K1432" s="16">
+      <c r="K1432" s="1">
         <v>46215</v>
       </c>
     </row>
-    <row r="1433" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1433" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1433" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1433" s="17" t="s">
+    <row r="1433" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1433" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1433" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1433" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="D1433" s="17" t="s">
+      <c r="D1433" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="E1433" s="17" t="s">
+      <c r="E1433" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F1433" s="17"/>
-      <c r="G1433" s="17"/>
-      <c r="H1433" s="17"/>
-      <c r="I1433" s="19" t="s">
+      <c r="F1433" s="2"/>
+      <c r="G1433" s="2"/>
+      <c r="H1433" s="2"/>
+      <c r="I1433" s="9" t="s">
         <v>788</v>
       </c>
-      <c r="J1433" s="18">
+      <c r="J1433" s="7">
         <v>1</v>
       </c>
-      <c r="K1433" s="16">
+      <c r="K1433" s="1">
         <v>46215</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1434" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1434" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1434" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="I1434" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1434" s="1">
+        <v>46217</v>
+      </c>
+      <c r="L1434" s="7" t="s">
+        <v>1450</v>
+      </c>
+      <c r="M1434" s="7">
+        <v>360</v>
+      </c>
+      <c r="N1434" s="7">
+        <v>9</v>
+      </c>
+      <c r="O1434" s="7">
+        <v>2.8559999999999999</v>
+      </c>
+      <c r="Q1434" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1435" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1435" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1435" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1435" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1435" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="K1435" s="1">
+        <v>46217</v>
+      </c>
+      <c r="L1435" s="7" t="s">
+        <v>1451</v>
+      </c>
+      <c r="M1435" s="7">
+        <v>746</v>
+      </c>
+      <c r="N1435" s="7">
+        <v>11</v>
+      </c>
+      <c r="O1435" s="7">
+        <v>4.74</v>
+      </c>
+      <c r="Q1435" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1436" s="7" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B1436" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1436" s="9" t="s">
+        <v>1449</v>
+      </c>
+      <c r="K1436" s="1">
+        <v>46218</v>
+      </c>
+      <c r="L1436" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="M1436" s="7">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1437" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1437" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1437" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1437" s="9" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K1437" s="1">
+        <v>46220</v>
+      </c>
+      <c r="M1437" s="7">
+        <v>200</v>
+      </c>
+      <c r="N1437" s="7">
+        <v>455</v>
+      </c>
+      <c r="O1437" s="7">
+        <v>7.82</v>
+      </c>
+      <c r="Q1437" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="U1437" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="V1437" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1438" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1438" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1438" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1438" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="K1438" s="1">
+        <v>46221</v>
+      </c>
+      <c r="L1438" s="7" t="s">
+        <v>1445</v>
+      </c>
+      <c r="M1438" s="7">
+        <v>432</v>
+      </c>
+      <c r="O1438" s="7">
+        <v>2.69</v>
+      </c>
+      <c r="Q1438" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1439" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1439" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1439" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1439" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1439" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="K1439" s="1">
+        <v>46221</v>
+      </c>
+      <c r="L1439" s="7" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M1439" s="7">
+        <v>801</v>
+      </c>
+      <c r="N1439" s="7">
+        <v>4</v>
+      </c>
+      <c r="O1439" s="7">
+        <v>5.05</v>
+      </c>
+      <c r="Q1439" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1440" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1440" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1440" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1440" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1440" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="K1440" s="1">
+        <v>46221</v>
+      </c>
+      <c r="L1440" s="7" t="s">
+        <v>1447</v>
+      </c>
+      <c r="M1440" s="7">
+        <v>813</v>
+      </c>
+      <c r="N1440" s="7">
+        <v>4</v>
+      </c>
+      <c r="O1440" s="7">
+        <v>5.43</v>
+      </c>
+      <c r="Q1440" s="7" t="s">
+        <v>1051</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA89FCAE-17D6-4D5D-9064-5188B73D0B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF541037-6E97-441C-A485-FDA3F13C7E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8240" uniqueCount="1457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8309" uniqueCount="1469">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4407,6 +4407,42 @@
   </si>
   <si>
     <t>xx</t>
+  </si>
+  <si>
+    <t>00:30:37.3</t>
+  </si>
+  <si>
+    <t>00:30:26.7</t>
+  </si>
+  <si>
+    <t>Gadmen Lodge</t>
+  </si>
+  <si>
+    <t>00:50:25.3</t>
+  </si>
+  <si>
+    <t>02:15:50.0</t>
+  </si>
+  <si>
+    <t>Oberzwirgi</t>
+  </si>
+  <si>
+    <t>Aussichtspunkt</t>
+  </si>
+  <si>
+    <t>00:39:50.5</t>
+  </si>
+  <si>
+    <t>00:45:33.2</t>
+  </si>
+  <si>
+    <t>00:31:45.9</t>
+  </si>
+  <si>
+    <t>00:29:21.9</t>
+  </si>
+  <si>
+    <t>00:31:57.7</t>
   </si>
 </sst>
 </file>
@@ -4942,8 +4978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Y1445"/>
+  <dimension ref="A1:Y1456"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="7" customWidth="1"/>
@@ -5051,7 +5086,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>51</v>
       </c>
@@ -5079,7 +5114,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>43</v>
       </c>
@@ -5099,7 +5134,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>70</v>
       </c>
@@ -5113,7 +5148,7 @@
         <v>37980</v>
       </c>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>70</v>
       </c>
@@ -5130,7 +5165,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
@@ -5150,7 +5185,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>70</v>
       </c>
@@ -5170,7 +5205,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>70</v>
       </c>
@@ -5190,7 +5225,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
@@ -5218,7 +5253,7 @@
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
@@ -5238,7 +5273,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>70</v>
       </c>
@@ -5261,7 +5296,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>70</v>
       </c>
@@ -5278,7 +5313,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>43</v>
       </c>
@@ -5313,7 +5348,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
@@ -5333,7 +5368,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>43</v>
       </c>
@@ -5591,7 +5626,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>43</v>
       </c>
@@ -5614,7 +5649,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>43</v>
       </c>
@@ -5637,7 +5672,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>70</v>
       </c>
@@ -5657,7 +5692,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>70</v>
       </c>
@@ -5691,7 +5726,7 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
         <v>70</v>
       </c>
@@ -5708,7 +5743,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>70</v>
       </c>
@@ -5737,7 +5772,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
         <v>70</v>
       </c>
@@ -5757,7 +5792,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>70</v>
       </c>
@@ -5777,7 +5812,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
         <v>70</v>
       </c>
@@ -5840,7 +5875,7 @@
       <c r="R34" s="5"/>
       <c r="S34" s="5"/>
     </row>
-    <row r="35" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
         <v>43</v>
       </c>
@@ -5863,7 +5898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>51</v>
       </c>
@@ -5891,7 +5926,7 @@
       <c r="R36" s="4"/>
       <c r="S36" s="4"/>
     </row>
-    <row r="37" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>51</v>
       </c>
@@ -5919,7 +5954,7 @@
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
     </row>
-    <row r="38" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
         <v>43</v>
       </c>
@@ -5948,7 +5983,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="39" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>43</v>
       </c>
@@ -5979,7 +6014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
         <v>70</v>
       </c>
@@ -5999,7 +6034,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
         <v>51</v>
       </c>
@@ -6027,7 +6062,7 @@
       <c r="R41" s="4"/>
       <c r="S41" s="4"/>
     </row>
-    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -6236,7 +6271,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
         <v>51</v>
       </c>
@@ -6300,7 +6335,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
         <v>70</v>
       </c>
@@ -6326,7 +6361,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
         <v>70</v>
       </c>
@@ -6346,7 +6381,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
         <v>70</v>
       </c>
@@ -6378,7 +6413,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
         <v>70</v>
       </c>
@@ -6415,7 +6450,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
         <v>51</v>
       </c>
@@ -6443,7 +6478,7 @@
       <c r="R55" s="4"/>
       <c r="S55" s="4"/>
     </row>
-    <row r="56" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
         <v>51</v>
       </c>
@@ -6507,7 +6542,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
         <v>51</v>
       </c>
@@ -6571,7 +6606,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
         <v>51</v>
       </c>
@@ -6635,7 +6670,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="62" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
         <v>70</v>
       </c>
@@ -6672,7 +6707,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="63" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
         <v>70</v>
       </c>
@@ -6734,7 +6769,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
         <v>51</v>
       </c>
@@ -6754,7 +6789,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
         <v>51</v>
       </c>
@@ -6782,7 +6817,7 @@
       <c r="R66" s="4"/>
       <c r="S66" s="4"/>
     </row>
-    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
         <v>51</v>
       </c>
@@ -6810,7 +6845,7 @@
       <c r="R67" s="4"/>
       <c r="S67" s="4"/>
     </row>
-    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
         <v>51</v>
       </c>
@@ -6838,7 +6873,7 @@
       <c r="R68" s="4"/>
       <c r="S68" s="4"/>
     </row>
-    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
         <v>51</v>
       </c>
@@ -6866,7 +6901,7 @@
       <c r="R69" s="4"/>
       <c r="S69" s="4"/>
     </row>
-    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
         <v>70</v>
       </c>
@@ -6892,7 +6927,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
         <v>70</v>
       </c>
@@ -6918,7 +6953,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
         <v>70</v>
       </c>
@@ -6944,7 +6979,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
         <v>51</v>
       </c>
@@ -6972,7 +7007,7 @@
       <c r="R73" s="4"/>
       <c r="S73" s="4"/>
     </row>
-    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
         <v>51</v>
       </c>
@@ -7000,7 +7035,7 @@
       <c r="R74" s="4"/>
       <c r="S74" s="4"/>
     </row>
-    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>51</v>
       </c>
@@ -7020,7 +7055,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>51</v>
       </c>
@@ -7040,7 +7075,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>51</v>
       </c>
@@ -7060,7 +7095,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>51</v>
       </c>
@@ -7080,7 +7115,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
         <v>51</v>
       </c>
@@ -7108,7 +7143,7 @@
       <c r="R79" s="4"/>
       <c r="S79" s="4"/>
     </row>
-    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>51</v>
       </c>
@@ -7180,7 +7215,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="7" t="s">
         <v>51</v>
       </c>
@@ -7208,7 +7243,7 @@
       <c r="R83" s="4"/>
       <c r="S83" s="4"/>
     </row>
-    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="7" t="s">
         <v>43</v>
       </c>
@@ -7228,7 +7263,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>51</v>
       </c>
@@ -7256,7 +7291,7 @@
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
     </row>
-    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>51</v>
       </c>
@@ -7276,7 +7311,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>51</v>
       </c>
@@ -7296,7 +7331,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>51</v>
       </c>
@@ -7316,7 +7351,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>51</v>
       </c>
@@ -7336,7 +7371,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>51</v>
       </c>
@@ -7356,7 +7391,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>51</v>
       </c>
@@ -7376,7 +7411,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="7" t="s">
         <v>70</v>
       </c>
@@ -7402,7 +7437,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
         <v>51</v>
       </c>
@@ -7464,7 +7499,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="7" t="s">
         <v>51</v>
       </c>
@@ -7484,7 +7519,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="7" t="s">
         <v>51</v>
       </c>
@@ -7504,7 +7539,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="7" t="s">
         <v>51</v>
       </c>
@@ -7524,7 +7559,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="7" t="s">
         <v>70</v>
       </c>
@@ -7550,7 +7585,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="7" t="s">
         <v>51</v>
       </c>
@@ -7570,7 +7605,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="7" t="s">
         <v>51</v>
       </c>
@@ -7590,7 +7625,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="101" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="7" t="s">
         <v>51</v>
       </c>
@@ -7610,7 +7645,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="102" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="7" t="s">
         <v>51</v>
       </c>
@@ -7630,7 +7665,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="103" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="7" t="s">
         <v>51</v>
       </c>
@@ -7650,7 +7685,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="7" t="s">
         <v>51</v>
       </c>
@@ -7678,7 +7713,7 @@
       <c r="R104" s="4"/>
       <c r="S104" s="4"/>
     </row>
-    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="7" t="s">
         <v>51</v>
       </c>
@@ -7709,7 +7744,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="7" t="s">
         <v>51</v>
       </c>
@@ -7729,7 +7764,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="107" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="7" t="s">
         <v>51</v>
       </c>
@@ -7757,7 +7792,7 @@
       <c r="R107" s="4"/>
       <c r="S107" s="4"/>
     </row>
-    <row r="108" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="7" t="s">
         <v>51</v>
       </c>
@@ -7788,7 +7823,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="7" t="s">
         <v>51</v>
       </c>
@@ -7841,7 +7876,7 @@
       <c r="R110" s="5"/>
       <c r="S110" s="5"/>
     </row>
-    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="7" t="s">
         <v>51</v>
       </c>
@@ -7869,7 +7904,7 @@
       <c r="R111" s="5"/>
       <c r="S111" s="5"/>
     </row>
-    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="7" t="s">
         <v>51</v>
       </c>
@@ -7928,7 +7963,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="114" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
         <v>51</v>
       </c>
@@ -7948,7 +7983,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="115" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
         <v>51</v>
       </c>
@@ -7968,7 +8003,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="116" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
         <v>51</v>
       </c>
@@ -8002,7 +8037,7 @@
         <v>43204</v>
       </c>
     </row>
-    <row r="118" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="7" t="s">
         <v>70</v>
       </c>
@@ -8174,7 +8209,7 @@
       <c r="R123" s="6"/>
       <c r="S123" s="6"/>
     </row>
-    <row r="124" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="7" t="s">
         <v>51</v>
       </c>
@@ -8202,7 +8237,7 @@
       <c r="R124" s="6"/>
       <c r="S124" s="6"/>
     </row>
-    <row r="125" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
         <v>51</v>
       </c>
@@ -8354,7 +8389,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>51</v>
       </c>
@@ -8436,7 +8471,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A133" s="7" t="s">
         <v>51</v>
       </c>
@@ -8646,7 +8681,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A141" s="7" t="s">
         <v>51</v>
       </c>
@@ -8669,7 +8704,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A142" s="7" t="s">
         <v>51</v>
       </c>
@@ -8689,7 +8724,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A143" s="7" t="s">
         <v>51</v>
       </c>
@@ -8878,7 +8913,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="150" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A150" s="7" t="s">
         <v>51</v>
       </c>
@@ -8901,7 +8936,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="151" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A151" s="7" t="s">
         <v>51</v>
       </c>
@@ -8924,7 +8959,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="152" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A152" s="7" t="s">
         <v>51</v>
       </c>
@@ -8947,7 +8982,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A153" s="7" t="s">
         <v>70</v>
       </c>
@@ -8973,7 +9008,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="154" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A154" s="7" t="s">
         <v>70</v>
       </c>
@@ -9007,7 +9042,7 @@
       <c r="R154" s="4"/>
       <c r="S154" s="4"/>
     </row>
-    <row r="155" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A155" s="7" t="s">
         <v>70</v>
       </c>
@@ -9038,7 +9073,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="156" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A156" s="7" t="s">
         <v>70</v>
       </c>
@@ -9067,7 +9102,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="157" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A157" s="7" t="s">
         <v>70</v>
       </c>
@@ -9101,7 +9136,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="158" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A158" s="7" t="s">
         <v>70</v>
       </c>
@@ -9135,7 +9170,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="159" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A159" s="7" t="s">
         <v>51</v>
       </c>
@@ -9155,7 +9190,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="160" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A160" s="7" t="s">
         <v>70</v>
       </c>
@@ -9189,7 +9224,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A161" s="7" t="s">
         <v>51</v>
       </c>
@@ -9209,7 +9244,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A162" s="7" t="s">
         <v>51</v>
       </c>
@@ -9232,7 +9267,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A163" s="7" t="s">
         <v>70</v>
       </c>
@@ -9266,7 +9301,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A164" s="7" t="s">
         <v>70</v>
       </c>
@@ -9297,7 +9332,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A165" s="7" t="s">
         <v>70</v>
       </c>
@@ -9331,7 +9366,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A166" s="7" t="s">
         <v>51</v>
       </c>
@@ -9354,7 +9389,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A167" s="7" t="s">
         <v>51</v>
       </c>
@@ -9374,7 +9409,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A168" s="7" t="s">
         <v>51</v>
       </c>
@@ -9397,7 +9432,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A169" s="7" t="s">
         <v>51</v>
       </c>
@@ -9420,7 +9455,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A170" s="7" t="s">
         <v>70</v>
       </c>
@@ -9454,7 +9489,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A171" s="7" t="s">
         <v>70</v>
       </c>
@@ -9491,7 +9526,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A172" s="7" t="s">
         <v>70</v>
       </c>
@@ -9580,7 +9615,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1" t="s">
         <v>148</v>
@@ -9598,7 +9633,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A176" s="7" t="s">
         <v>51</v>
       </c>
@@ -9618,7 +9653,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>51</v>
       </c>
@@ -9638,7 +9673,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A178" s="7" t="s">
         <v>51</v>
       </c>
@@ -9661,7 +9696,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A179" s="7" t="s">
         <v>51</v>
       </c>
@@ -9709,7 +9744,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
         <v>224</v>
       </c>
@@ -9798,7 +9833,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
         <v>51</v>
       </c>
@@ -9967,7 +10002,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A190" s="7" t="s">
         <v>51</v>
       </c>
@@ -10043,7 +10078,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A193" s="7" t="s">
         <v>51</v>
       </c>
@@ -10095,7 +10130,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
         <v>224</v>
       </c>
@@ -10147,7 +10182,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A197" s="7" t="s">
         <v>51</v>
       </c>
@@ -10172,7 +10207,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>224</v>
       </c>
@@ -10200,7 +10235,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
         <v>51</v>
       </c>
@@ -10223,7 +10258,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A200" s="7" t="s">
         <v>51</v>
       </c>
@@ -10243,7 +10278,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A201" s="7" t="s">
         <v>70</v>
       </c>
@@ -10280,7 +10315,7 @@
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
     </row>
-    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A202" s="7" t="s">
         <v>70</v>
       </c>
@@ -10320,7 +10355,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A203" s="7" t="s">
         <v>70</v>
       </c>
@@ -10360,7 +10395,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A204" s="7" t="s">
         <v>70</v>
       </c>
@@ -10391,7 +10426,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="s">
         <v>51</v>
       </c>
@@ -10411,7 +10446,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>51</v>
       </c>
@@ -10643,7 +10678,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A215" s="7" t="s">
         <v>51</v>
       </c>
@@ -10696,7 +10731,7 @@
       <c r="O216" s="4"/>
       <c r="P216" s="4"/>
     </row>
-    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
         <v>224</v>
       </c>
@@ -10766,7 +10801,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>224</v>
       </c>
@@ -11234,7 +11269,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A238" s="7" t="s">
         <v>224</v>
       </c>
@@ -11564,7 +11599,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A251" s="7" t="s">
         <v>51</v>
       </c>
@@ -11616,7 +11651,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
         <v>224</v>
       </c>
@@ -11775,7 +11810,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" s="7" t="s">
         <v>51</v>
       </c>
@@ -11984,7 +12019,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268" s="7" t="s">
         <v>51</v>
       </c>
@@ -12009,7 +12044,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
         <v>224</v>
       </c>
@@ -12342,7 +12377,7 @@
         <v>44060</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" s="7" t="s">
         <v>51</v>
       </c>
@@ -12716,7 +12751,7 @@
         <v>44082</v>
       </c>
     </row>
-    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
         <v>51</v>
       </c>
@@ -12838,7 +12873,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="302" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302" s="7" t="s">
         <v>51</v>
       </c>
@@ -12864,7 +12899,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="303" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303" s="7" t="s">
         <v>51</v>
       </c>
@@ -12887,7 +12922,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304" s="7" t="s">
         <v>51</v>
       </c>
@@ -12910,7 +12945,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A305" s="7" t="s">
         <v>51</v>
       </c>
@@ -13077,7 +13112,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A312" s="7" t="s">
         <v>51</v>
       </c>
@@ -13258,7 +13293,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="319" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
         <v>224</v>
       </c>
@@ -13283,7 +13318,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A320" s="7" t="s">
         <v>70</v>
       </c>
@@ -13309,7 +13344,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="321" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A321" s="7" t="s">
         <v>70</v>
       </c>
@@ -13338,7 +13373,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="322" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A322" s="7" t="s">
         <v>70</v>
       </c>
@@ -13370,7 +13405,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="323" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A323" s="7" t="s">
         <v>366</v>
       </c>
@@ -13396,7 +13431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A324" s="7" t="s">
         <v>70</v>
       </c>
@@ -13433,7 +13468,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="325" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A325" s="7" t="s">
         <v>366</v>
       </c>
@@ -13459,7 +13494,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="326" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A326" s="7" t="s">
         <v>366</v>
       </c>
@@ -13479,7 +13514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A327" s="7" t="s">
         <v>366</v>
       </c>
@@ -13502,7 +13537,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="328" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A328" s="7" t="s">
         <v>70</v>
       </c>
@@ -13528,7 +13563,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="329" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A329" s="7" t="s">
         <v>366</v>
       </c>
@@ -13545,7 +13580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A330" s="7" t="s">
         <v>70</v>
       </c>
@@ -13574,7 +13609,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="331" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A331" s="7" t="s">
         <v>366</v>
       </c>
@@ -13597,7 +13632,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="332" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A332" s="7" t="s">
         <v>366</v>
       </c>
@@ -13617,7 +13652,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="333" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A333" s="7" t="s">
         <v>366</v>
       </c>
@@ -13637,7 +13672,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="334" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A334" s="7" t="s">
         <v>366</v>
       </c>
@@ -13657,7 +13692,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="335" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A335" s="7" t="s">
         <v>366</v>
       </c>
@@ -13680,7 +13715,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="336" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A336" s="7" t="s">
         <v>51</v>
       </c>
@@ -13703,7 +13738,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="337" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A337" s="7" t="s">
         <v>366</v>
       </c>
@@ -13726,7 +13761,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="338" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A338" s="7" t="s">
         <v>366</v>
       </c>
@@ -13749,7 +13784,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="339" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A339" s="7" t="s">
         <v>366</v>
       </c>
@@ -13766,7 +13801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A340" s="7" t="s">
         <v>366</v>
       </c>
@@ -13783,7 +13818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A341" s="7" t="s">
         <v>366</v>
       </c>
@@ -13803,7 +13838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A342" s="7" t="s">
         <v>366</v>
       </c>
@@ -13823,7 +13858,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="343" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A343" s="7" t="s">
         <v>366</v>
       </c>
@@ -13840,7 +13875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A344" s="7" t="s">
         <v>70</v>
       </c>
@@ -13872,7 +13907,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="345" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A345" s="7" t="s">
         <v>366</v>
       </c>
@@ -13892,7 +13927,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="346" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A346" s="7" t="s">
         <v>70</v>
       </c>
@@ -13921,7 +13956,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="347" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A347" s="7" t="s">
         <v>366</v>
       </c>
@@ -13944,7 +13979,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="348" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A348" s="7" t="s">
         <v>70</v>
       </c>
@@ -13973,7 +14008,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="349" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A349" s="7" t="s">
         <v>366</v>
       </c>
@@ -13999,7 +14034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A350" s="7" t="s">
         <v>366</v>
       </c>
@@ -14016,7 +14051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A351" s="7" t="s">
         <v>366</v>
       </c>
@@ -14039,7 +14074,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="352" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A352" s="7" t="s">
         <v>366</v>
       </c>
@@ -14056,7 +14091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A353" s="7" t="s">
         <v>70</v>
       </c>
@@ -14087,7 +14122,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A354" s="7" t="s">
         <v>366</v>
       </c>
@@ -14110,7 +14145,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A355" s="7" t="s">
         <v>70</v>
       </c>
@@ -14139,7 +14174,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A356" s="7" t="s">
         <v>366</v>
       </c>
@@ -14156,7 +14191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A357" s="7" t="s">
         <v>366</v>
       </c>
@@ -14179,7 +14214,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A358" s="7" t="s">
         <v>70</v>
       </c>
@@ -14211,7 +14246,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A359" s="7" t="s">
         <v>70</v>
       </c>
@@ -14240,7 +14275,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A360" s="7" t="s">
         <v>366</v>
       </c>
@@ -14266,7 +14301,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A361" s="7" t="s">
         <v>70</v>
       </c>
@@ -14298,7 +14333,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A362" s="7" t="s">
         <v>366</v>
       </c>
@@ -14318,7 +14353,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A363" s="7" t="s">
         <v>366</v>
       </c>
@@ -14347,7 +14382,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A364" s="7" t="s">
         <v>366</v>
       </c>
@@ -14376,7 +14411,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A365" s="7" t="s">
         <v>70</v>
       </c>
@@ -14402,7 +14437,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A366" s="7" t="s">
         <v>70</v>
       </c>
@@ -14436,7 +14471,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A367" s="7" t="s">
         <v>70</v>
       </c>
@@ -14465,7 +14500,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A368" s="7" t="s">
         <v>70</v>
       </c>
@@ -14499,7 +14534,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A369" s="7" t="s">
         <v>366</v>
       </c>
@@ -14522,7 +14557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A370" s="7" t="s">
         <v>70</v>
       </c>
@@ -14571,7 +14606,7 @@
         <v>44257</v>
       </c>
     </row>
-    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A372" s="7" t="s">
         <v>366</v>
       </c>
@@ -14597,7 +14632,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A373" s="7" t="s">
         <v>70</v>
       </c>
@@ -14623,7 +14658,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A374" s="7" t="s">
         <v>70</v>
       </c>
@@ -14657,7 +14692,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A375" s="7" t="s">
         <v>51</v>
       </c>
@@ -14677,7 +14712,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A376" s="7" t="s">
         <v>70</v>
       </c>
@@ -14703,7 +14738,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A377" s="7" t="s">
         <v>70</v>
       </c>
@@ -14732,7 +14767,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A378" s="7" t="s">
         <v>366</v>
       </c>
@@ -14752,7 +14787,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A379" s="7" t="s">
         <v>70</v>
       </c>
@@ -14784,7 +14819,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A380" s="7" t="s">
         <v>366</v>
       </c>
@@ -14801,7 +14836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A381" s="7" t="s">
         <v>70</v>
       </c>
@@ -14827,7 +14862,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A382" s="7" t="s">
         <v>366</v>
       </c>
@@ -14850,7 +14885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A383" s="7" t="s">
         <v>70</v>
       </c>
@@ -14881,7 +14916,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A384" s="7" t="s">
         <v>70</v>
       </c>
@@ -14910,7 +14945,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="385" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A385" s="7" t="s">
         <v>70</v>
       </c>
@@ -14936,7 +14971,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="386" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A386" s="7" t="s">
         <v>70</v>
       </c>
@@ -14965,7 +15000,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="387" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A387" s="7" t="s">
         <v>70</v>
       </c>
@@ -14991,7 +15026,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="388" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A388" s="7" t="s">
         <v>70</v>
       </c>
@@ -15028,7 +15063,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="389" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A389" s="7" t="s">
         <v>70</v>
       </c>
@@ -15057,7 +15092,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="390" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A390" s="7" t="s">
         <v>70</v>
       </c>
@@ -15091,7 +15126,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="391" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A391" s="7" t="s">
         <v>70</v>
       </c>
@@ -15122,7 +15157,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="392" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A392" s="7" t="s">
         <v>70</v>
       </c>
@@ -15220,7 +15255,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="396" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A396" s="7" t="s">
         <v>70</v>
       </c>
@@ -15249,7 +15284,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="397" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A397" s="7" t="s">
         <v>70</v>
       </c>
@@ -15356,7 +15391,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A401" s="7" t="s">
         <v>70</v>
       </c>
@@ -15414,7 +15449,7 @@
         <v>44310</v>
       </c>
     </row>
-    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A403" s="7" t="s">
         <v>70</v>
       </c>
@@ -15532,7 +15567,7 @@
         <v>44319</v>
       </c>
     </row>
-    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A408" s="7" t="s">
         <v>70</v>
       </c>
@@ -15561,7 +15596,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A409" s="7" t="s">
         <v>70</v>
       </c>
@@ -15607,7 +15642,7 @@
         <v>44329</v>
       </c>
     </row>
-    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A411" s="7" t="s">
         <v>70</v>
       </c>
@@ -15762,7 +15797,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A418" s="7" t="s">
         <v>51</v>
       </c>
@@ -15822,7 +15857,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A421" s="7" t="s">
         <v>70</v>
       </c>
@@ -15894,7 +15929,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A424" s="7" t="s">
         <v>70</v>
       </c>
@@ -15923,7 +15958,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A425" s="7" t="s">
         <v>70</v>
       </c>
@@ -15952,7 +15987,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A426" s="7" t="s">
         <v>70</v>
       </c>
@@ -16974,7 +17009,7 @@
         <v>44404</v>
       </c>
     </row>
-    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A469" s="7" t="s">
         <v>51</v>
       </c>
@@ -17014,7 +17049,7 @@
         <v>44411</v>
       </c>
     </row>
-    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A471" s="7" t="s">
         <v>51</v>
       </c>
@@ -17161,7 +17196,7 @@
         <v>44420</v>
       </c>
     </row>
-    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A477" s="7" t="s">
         <v>51</v>
       </c>
@@ -17184,7 +17219,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A478" s="7" t="s">
         <v>51</v>
       </c>
@@ -17281,7 +17316,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A482" s="7" t="s">
         <v>51</v>
       </c>
@@ -17304,7 +17339,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A483" s="7" t="s">
         <v>51</v>
       </c>
@@ -17347,7 +17382,7 @@
         <v>44439</v>
       </c>
     </row>
-    <row r="485" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A485" s="7" t="s">
         <v>51</v>
       </c>
@@ -17561,7 +17596,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A494" s="7" t="s">
         <v>51</v>
       </c>
@@ -17581,7 +17616,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A495" s="7" t="s">
         <v>51</v>
       </c>
@@ -17649,7 +17684,7 @@
         <v>44449</v>
       </c>
     </row>
-    <row r="498" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A498" s="7" t="s">
         <v>51</v>
       </c>
@@ -17774,7 +17809,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="503" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A503" s="7" t="s">
         <v>51</v>
       </c>
@@ -17799,7 +17834,7 @@
       <c r="O503" s="4"/>
       <c r="P503" s="4"/>
     </row>
-    <row r="504" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A504" s="7" t="s">
         <v>43</v>
       </c>
@@ -17834,7 +17869,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="505" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A505" s="7" t="s">
         <v>51</v>
       </c>
@@ -17896,7 +17931,7 @@
         <v>44471</v>
       </c>
     </row>
-    <row r="508" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A508" s="7" t="s">
         <v>43</v>
       </c>
@@ -17928,7 +17963,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="509" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A509" s="7" t="s">
         <v>43</v>
       </c>
@@ -17983,7 +18018,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="511" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A511" s="7" t="s">
         <v>43</v>
       </c>
@@ -18154,7 +18189,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="518" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A518" s="7" t="s">
         <v>43</v>
       </c>
@@ -18343,7 +18378,7 @@
         <v>44512</v>
       </c>
     </row>
-    <row r="526" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A526" s="7" t="s">
         <v>51</v>
       </c>
@@ -18409,7 +18444,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="529" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A529" s="7" t="s">
         <v>51</v>
       </c>
@@ -18461,7 +18496,7 @@
       <c r="O530" s="9"/>
       <c r="P530" s="9"/>
     </row>
-    <row r="531" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A531" s="1" t="s">
         <v>224</v>
       </c>
@@ -18514,7 +18549,7 @@
         <v>44524</v>
       </c>
     </row>
-    <row r="533" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A533" s="7" t="s">
         <v>51</v>
       </c>
@@ -18534,7 +18569,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="534" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A534" s="7" t="s">
         <v>70</v>
       </c>
@@ -18563,7 +18598,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="535" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A535" s="7" t="s">
         <v>366</v>
       </c>
@@ -18583,7 +18618,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="536" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A536" s="7" t="s">
         <v>366</v>
       </c>
@@ -18609,7 +18644,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="537" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A537" s="7" t="s">
         <v>70</v>
       </c>
@@ -18635,7 +18670,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="538" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A538" s="7" t="s">
         <v>70</v>
       </c>
@@ -18661,7 +18696,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="539" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A539" s="7" t="s">
         <v>366</v>
       </c>
@@ -18684,7 +18719,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="540" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A540" s="7" t="s">
         <v>70</v>
       </c>
@@ -18710,7 +18745,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="541" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A541" s="7" t="s">
         <v>70</v>
       </c>
@@ -18745,7 +18780,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="542" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A542" s="7" t="s">
         <v>70</v>
       </c>
@@ -18774,7 +18809,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="543" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A543" s="7" t="s">
         <v>70</v>
       </c>
@@ -18800,7 +18835,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="544" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A544" s="7" t="s">
         <v>51</v>
       </c>
@@ -18820,7 +18855,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A545" s="7" t="s">
         <v>366</v>
       </c>
@@ -18843,7 +18878,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A546" s="7" t="s">
         <v>70</v>
       </c>
@@ -18872,7 +18907,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A547" s="7" t="s">
         <v>70</v>
       </c>
@@ -18901,7 +18936,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A548" s="7" t="s">
         <v>366</v>
       </c>
@@ -18924,7 +18959,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A549" s="7" t="s">
         <v>70</v>
       </c>
@@ -18956,7 +18991,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A550" s="7" t="s">
         <v>51</v>
       </c>
@@ -18976,7 +19011,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A551" s="7" t="s">
         <v>51</v>
       </c>
@@ -18996,7 +19031,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A552" s="7" t="s">
         <v>366</v>
       </c>
@@ -19019,7 +19054,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A553" s="7" t="s">
         <v>70</v>
       </c>
@@ -19056,7 +19091,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A554" s="7" t="s">
         <v>70</v>
       </c>
@@ -19090,7 +19125,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A555" s="7" t="s">
         <v>70</v>
       </c>
@@ -19116,7 +19151,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A556" s="7" t="s">
         <v>70</v>
       </c>
@@ -19142,7 +19177,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A557" s="7" t="s">
         <v>366</v>
       </c>
@@ -19165,7 +19200,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A558" s="7" t="s">
         <v>70</v>
       </c>
@@ -19191,7 +19226,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A559" s="7" t="s">
         <v>70</v>
       </c>
@@ -19223,7 +19258,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="560" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A560" s="7" t="s">
         <v>366</v>
       </c>
@@ -19252,7 +19287,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A561" s="7" t="s">
         <v>70</v>
       </c>
@@ -19281,7 +19316,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A562" s="7" t="s">
         <v>366</v>
       </c>
@@ -19298,7 +19333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A563" s="7" t="s">
         <v>70</v>
       </c>
@@ -19324,7 +19359,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="564" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A564" s="7" t="s">
         <v>70</v>
       </c>
@@ -19356,7 +19391,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="565" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A565" s="7" t="s">
         <v>366</v>
       </c>
@@ -19385,7 +19420,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="566" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A566" s="7" t="s">
         <v>70</v>
       </c>
@@ -19414,7 +19449,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="567" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A567" s="7" t="s">
         <v>366</v>
       </c>
@@ -19437,7 +19472,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="568" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A568" s="7" t="s">
         <v>366</v>
       </c>
@@ -19457,7 +19492,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="569" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A569" s="7" t="s">
         <v>70</v>
       </c>
@@ -19486,7 +19521,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="570" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A570" s="7" t="s">
         <v>70</v>
       </c>
@@ -19515,7 +19550,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="571" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A571" s="7" t="s">
         <v>366</v>
       </c>
@@ -19538,7 +19573,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="572" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A572" s="7" t="s">
         <v>70</v>
       </c>
@@ -19567,7 +19602,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="573" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A573" s="7" t="s">
         <v>70</v>
       </c>
@@ -19590,7 +19625,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="574" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A574" s="7" t="s">
         <v>366</v>
       </c>
@@ -19610,7 +19645,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="575" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A575" s="7" t="s">
         <v>366</v>
       </c>
@@ -19630,7 +19665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="576" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A576" s="7" t="s">
         <v>366</v>
       </c>
@@ -19659,7 +19694,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="577" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A577" s="7" t="s">
         <v>70</v>
       </c>
@@ -19690,7 +19725,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="578" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A578" s="7" t="s">
         <v>70</v>
       </c>
@@ -19721,7 +19756,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="579" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A579" s="7" t="s">
         <v>70</v>
       </c>
@@ -19747,7 +19782,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="580" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A580" s="7" t="s">
         <v>70</v>
       </c>
@@ -19790,7 +19825,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="581" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A581" s="7" t="s">
         <v>70</v>
       </c>
@@ -19819,7 +19854,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="582" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A582" s="7" t="s">
         <v>70</v>
       </c>
@@ -19854,7 +19889,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="583" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A583" s="7" t="s">
         <v>366</v>
       </c>
@@ -19880,7 +19915,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="584" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A584" s="7" t="s">
         <v>70</v>
       </c>
@@ -19915,7 +19950,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="585" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A585" s="7" t="s">
         <v>366</v>
       </c>
@@ -19932,7 +19967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A586" s="7" t="s">
         <v>366</v>
       </c>
@@ -19958,7 +19993,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="587" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A587" s="7" t="s">
         <v>366</v>
       </c>
@@ -19975,7 +20010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A588" s="7" t="s">
         <v>70</v>
       </c>
@@ -20038,7 +20073,7 @@
         <v>44637</v>
       </c>
     </row>
-    <row r="591" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A591" s="7" t="s">
         <v>366</v>
       </c>
@@ -20061,7 +20096,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="592" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A592" s="7" t="s">
         <v>70</v>
       </c>
@@ -20132,7 +20167,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="595" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A595" s="7" t="s">
         <v>366</v>
       </c>
@@ -20166,7 +20201,7 @@
         <v>44649</v>
       </c>
     </row>
-    <row r="597" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A597" s="7" t="s">
         <v>70</v>
       </c>
@@ -20212,7 +20247,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="599" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A599" s="7" t="s">
         <v>70</v>
       </c>
@@ -20238,7 +20273,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="600" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A600" s="7" t="s">
         <v>70</v>
       </c>
@@ -20264,7 +20299,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="601" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A601" s="7" t="s">
         <v>70</v>
       </c>
@@ -20313,7 +20348,7 @@
         <v>44668</v>
       </c>
     </row>
-    <row r="603" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A603" s="7" t="s">
         <v>51</v>
       </c>
@@ -20333,7 +20368,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="604" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A604" s="7" t="s">
         <v>70</v>
       </c>
@@ -20362,7 +20397,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="605" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A605" s="7" t="s">
         <v>70</v>
       </c>
@@ -20524,7 +20559,7 @@
         <v>44847</v>
       </c>
     </row>
-    <row r="612" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A612" s="7" t="s">
         <v>43</v>
       </c>
@@ -20956,7 +20991,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="630" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A630" s="7" t="s">
         <v>43</v>
       </c>
@@ -21122,7 +21157,7 @@
         <v>44882</v>
       </c>
     </row>
-    <row r="637" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A637" s="7" t="s">
         <v>43</v>
       </c>
@@ -21142,7 +21177,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="638" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A638" s="7" t="s">
         <v>43</v>
       </c>
@@ -21162,7 +21197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="639" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A639" s="7" t="s">
         <v>43</v>
       </c>
@@ -21179,7 +21214,7 @@
         <v>44897</v>
       </c>
     </row>
-    <row r="640" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A640" s="7" t="s">
         <v>43</v>
       </c>
@@ -21196,7 +21231,7 @@
         <v>44905</v>
       </c>
     </row>
-    <row r="641" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A641" s="7" t="s">
         <v>43</v>
       </c>
@@ -21216,7 +21251,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="642" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A642" s="7" t="s">
         <v>43</v>
       </c>
@@ -21233,7 +21268,7 @@
         <v>44911</v>
       </c>
     </row>
-    <row r="643" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A643" s="7" t="s">
         <v>720</v>
       </c>
@@ -21250,7 +21285,7 @@
         <v>44912</v>
       </c>
     </row>
-    <row r="644" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A644" s="7" t="s">
         <v>43</v>
       </c>
@@ -21270,7 +21305,7 @@
         <v>44913</v>
       </c>
     </row>
-    <row r="645" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A645" s="7" t="s">
         <v>43</v>
       </c>
@@ -21287,7 +21322,7 @@
         <v>44914</v>
       </c>
     </row>
-    <row r="646" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A646" s="7" t="s">
         <v>43</v>
       </c>
@@ -21304,7 +21339,7 @@
         <v>44915</v>
       </c>
     </row>
-    <row r="647" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A647" s="7" t="s">
         <v>43</v>
       </c>
@@ -21327,7 +21362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="648" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A648" s="7" t="s">
         <v>43</v>
       </c>
@@ -21347,7 +21382,7 @@
         <v>44920</v>
       </c>
     </row>
-    <row r="649" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A649" s="7" t="s">
         <v>43</v>
       </c>
@@ -21364,7 +21399,7 @@
         <v>44921</v>
       </c>
     </row>
-    <row r="650" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A650" s="7" t="s">
         <v>43</v>
       </c>
@@ -21381,7 +21416,7 @@
         <v>44922</v>
       </c>
     </row>
-    <row r="651" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A651" s="7" t="s">
         <v>43</v>
       </c>
@@ -21410,7 +21445,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="652" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A652" s="7" t="s">
         <v>51</v>
       </c>
@@ -21427,7 +21462,7 @@
         <v>44924</v>
       </c>
     </row>
-    <row r="653" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A653" s="7" t="s">
         <v>43</v>
       </c>
@@ -21459,7 +21494,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="654" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A654" s="7" t="s">
         <v>51</v>
       </c>
@@ -21476,7 +21511,7 @@
         <v>44927</v>
       </c>
     </row>
-    <row r="655" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A655" s="7" t="s">
         <v>43</v>
       </c>
@@ -21499,7 +21534,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="656" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A656" s="7" t="s">
         <v>43</v>
       </c>
@@ -21522,7 +21557,7 @@
         <v>44934</v>
       </c>
     </row>
-    <row r="657" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A657" s="7" t="s">
         <v>43</v>
       </c>
@@ -21539,7 +21574,7 @@
         <v>44940</v>
       </c>
     </row>
-    <row r="658" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A658" s="7" t="s">
         <v>43</v>
       </c>
@@ -21556,7 +21591,7 @@
         <v>44942</v>
       </c>
     </row>
-    <row r="659" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A659" s="7" t="s">
         <v>43</v>
       </c>
@@ -21573,7 +21608,7 @@
         <v>44946</v>
       </c>
     </row>
-    <row r="660" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A660" s="7" t="s">
         <v>43</v>
       </c>
@@ -21593,7 +21628,7 @@
         <v>44947</v>
       </c>
     </row>
-    <row r="661" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A661" s="7" t="s">
         <v>43</v>
       </c>
@@ -21610,7 +21645,7 @@
         <v>44950</v>
       </c>
     </row>
-    <row r="662" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A662" s="7" t="s">
         <v>43</v>
       </c>
@@ -21627,7 +21662,7 @@
         <v>44953</v>
       </c>
     </row>
-    <row r="663" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A663" s="7" t="s">
         <v>43</v>
       </c>
@@ -21650,7 +21685,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="664" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A664" s="7" t="s">
         <v>43</v>
       </c>
@@ -21673,7 +21708,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="665" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A665" s="7" t="s">
         <v>43</v>
       </c>
@@ -21690,7 +21725,7 @@
         <v>44959</v>
       </c>
     </row>
-    <row r="666" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A666" s="7" t="s">
         <v>43</v>
       </c>
@@ -21716,7 +21751,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="667" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A667" s="7" t="s">
         <v>43</v>
       </c>
@@ -21739,7 +21774,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="668" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A668" s="7" t="s">
         <v>43</v>
       </c>
@@ -21762,7 +21797,7 @@
         <v>44962</v>
       </c>
     </row>
-    <row r="669" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A669" s="7" t="s">
         <v>43</v>
       </c>
@@ -21782,7 +21817,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="670" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A670" s="7" t="s">
         <v>43</v>
       </c>
@@ -21802,7 +21837,7 @@
         <v>44969</v>
       </c>
     </row>
-    <row r="671" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A671" s="7" t="s">
         <v>43</v>
       </c>
@@ -21822,7 +21857,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="672" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A672" s="7" t="s">
         <v>43</v>
       </c>
@@ -21926,7 +21961,7 @@
         <v>44979</v>
       </c>
     </row>
-    <row r="677" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A677" s="7" t="s">
         <v>43</v>
       </c>
@@ -21943,7 +21978,7 @@
         <v>44981</v>
       </c>
     </row>
-    <row r="678" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A678" s="7" t="s">
         <v>43</v>
       </c>
@@ -21960,7 +21995,7 @@
         <v>44985</v>
       </c>
     </row>
-    <row r="679" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A679" s="7" t="s">
         <v>43</v>
       </c>
@@ -21977,7 +22012,7 @@
         <v>44989</v>
       </c>
     </row>
-    <row r="680" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A680" s="7" t="s">
         <v>43</v>
       </c>
@@ -21994,7 +22029,7 @@
         <v>44993</v>
       </c>
     </row>
-    <row r="681" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A681" s="7" t="s">
         <v>43</v>
       </c>
@@ -22011,7 +22046,7 @@
         <v>44995</v>
       </c>
     </row>
-    <row r="682" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A682" s="7" t="s">
         <v>43</v>
       </c>
@@ -22071,7 +22106,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="685" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A685" s="7" t="s">
         <v>43</v>
       </c>
@@ -22131,7 +22166,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="688" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A688" s="7" t="s">
         <v>51</v>
       </c>
@@ -22148,7 +22183,7 @@
         <v>45011</v>
       </c>
     </row>
-    <row r="689" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A689" s="7" t="s">
         <v>51</v>
       </c>
@@ -22168,7 +22203,7 @@
         <v>45020</v>
       </c>
     </row>
-    <row r="690" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A690" s="7" t="s">
         <v>43</v>
       </c>
@@ -22205,7 +22240,7 @@
         <v>45022</v>
       </c>
     </row>
-    <row r="692" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A692" s="7" t="s">
         <v>43</v>
       </c>
@@ -22265,7 +22300,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="695" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A695" s="7" t="s">
         <v>51</v>
       </c>
@@ -22282,7 +22317,7 @@
         <v>45030</v>
       </c>
     </row>
-    <row r="696" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A696" s="7" t="s">
         <v>51</v>
       </c>
@@ -22299,7 +22334,7 @@
         <v>45031</v>
       </c>
     </row>
-    <row r="697" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A697" s="7" t="s">
         <v>51</v>
       </c>
@@ -22376,7 +22411,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="701" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A701" s="7" t="s">
         <v>51</v>
       </c>
@@ -22416,7 +22451,7 @@
         <v>45046</v>
       </c>
     </row>
-    <row r="703" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A703" s="7" t="s">
         <v>70</v>
       </c>
@@ -22442,7 +22477,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="704" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A704" s="7" t="s">
         <v>51</v>
       </c>
@@ -22462,7 +22497,7 @@
         <v>45056</v>
       </c>
     </row>
-    <row r="705" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A705" s="7" t="s">
         <v>51</v>
       </c>
@@ -22482,7 +22517,7 @@
         <v>45057</v>
       </c>
     </row>
-    <row r="706" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A706" s="7" t="s">
         <v>51</v>
       </c>
@@ -22499,7 +22534,7 @@
         <v>45059</v>
       </c>
     </row>
-    <row r="707" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A707" s="7" t="s">
         <v>51</v>
       </c>
@@ -22593,7 +22628,7 @@
         <v>45072</v>
       </c>
     </row>
-    <row r="712" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A712" s="7" t="s">
         <v>762</v>
       </c>
@@ -22756,7 +22791,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="720" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A720" s="7" t="s">
         <v>51</v>
       </c>
@@ -22799,7 +22834,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="722" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A722" s="1" t="s">
         <v>224</v>
       </c>
@@ -22866,7 +22901,7 @@
         <v>45085</v>
       </c>
     </row>
-    <row r="725" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A725" s="7" t="s">
         <v>762</v>
       </c>
@@ -22889,7 +22924,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="726" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A726" s="7" t="s">
         <v>762</v>
       </c>
@@ -22977,7 +23012,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="730" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A730" s="7" t="s">
         <v>51</v>
       </c>
@@ -22997,7 +23032,7 @@
         <v>45100</v>
       </c>
     </row>
-    <row r="731" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A731" s="7" t="s">
         <v>43</v>
       </c>
@@ -23017,7 +23052,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="732" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A732" s="7" t="s">
         <v>762</v>
       </c>
@@ -23108,7 +23143,7 @@
         <v>45110</v>
       </c>
     </row>
-    <row r="737" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A737" s="7" t="s">
         <v>43</v>
       </c>
@@ -23134,7 +23169,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="738" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A738" s="7" t="s">
         <v>51</v>
       </c>
@@ -23174,7 +23209,7 @@
         <v>45113</v>
       </c>
     </row>
-    <row r="740" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A740" s="7" t="s">
         <v>762</v>
       </c>
@@ -23294,7 +23329,7 @@
         <v>45122</v>
       </c>
     </row>
-    <row r="746" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A746" s="7" t="s">
         <v>51</v>
       </c>
@@ -23314,7 +23349,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="747" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A747" s="7" t="s">
         <v>43</v>
       </c>
@@ -23343,7 +23378,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="748" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A748" s="7" t="s">
         <v>43</v>
       </c>
@@ -23372,7 +23407,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="749" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A749" s="7" t="s">
         <v>51</v>
       </c>
@@ -23392,7 +23427,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="750" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A750" s="7" t="s">
         <v>51</v>
       </c>
@@ -23526,7 +23561,7 @@
         <v>45163</v>
       </c>
     </row>
-    <row r="757" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A757" s="7" t="s">
         <v>51</v>
       </c>
@@ -23546,7 +23581,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="758" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A758" s="7" t="s">
         <v>51</v>
       </c>
@@ -23566,7 +23601,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="759" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A759" s="7" t="s">
         <v>51</v>
       </c>
@@ -23626,7 +23661,7 @@
         <v>45179</v>
       </c>
     </row>
-    <row r="762" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A762" s="7" t="s">
         <v>51</v>
       </c>
@@ -23646,7 +23681,7 @@
         <v>45181</v>
       </c>
     </row>
-    <row r="763" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A763" s="7" t="s">
         <v>51</v>
       </c>
@@ -23723,7 +23758,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="767" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A767" s="7" t="s">
         <v>43</v>
       </c>
@@ -23932,7 +23967,7 @@
         <v>45211</v>
       </c>
     </row>
-    <row r="777" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A777" s="7" t="s">
         <v>51</v>
       </c>
@@ -23952,7 +23987,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="778" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A778" s="7" t="s">
         <v>762</v>
       </c>
@@ -23969,7 +24004,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="779" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A779" s="7" t="s">
         <v>51</v>
       </c>
@@ -23989,7 +24024,7 @@
         <v>45225</v>
       </c>
     </row>
-    <row r="780" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A780" s="7" t="s">
         <v>51</v>
       </c>
@@ -24006,7 +24041,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="781" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A781" s="7" t="s">
         <v>51</v>
       </c>
@@ -24023,7 +24058,7 @@
         <v>45242</v>
       </c>
     </row>
-    <row r="782" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A782" s="7" t="s">
         <v>70</v>
       </c>
@@ -24055,7 +24090,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="783" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A783" s="7" t="s">
         <v>70</v>
       </c>
@@ -24084,7 +24119,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="784" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A784" s="7" t="s">
         <v>70</v>
       </c>
@@ -24110,7 +24145,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="785" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A785" s="7" t="s">
         <v>70</v>
       </c>
@@ -24139,7 +24174,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="786" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A786" s="7" t="s">
         <v>366</v>
       </c>
@@ -24165,7 +24200,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="787" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A787" s="7" t="s">
         <v>51</v>
       </c>
@@ -24182,7 +24217,7 @@
         <v>45273</v>
       </c>
     </row>
-    <row r="788" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A788" s="7" t="s">
         <v>70</v>
       </c>
@@ -24214,7 +24249,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="789" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A789" s="7" t="s">
         <v>366</v>
       </c>
@@ -24237,7 +24272,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="790" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A790" s="7" t="s">
         <v>51</v>
       </c>
@@ -24257,7 +24292,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="791" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A791" s="7" t="s">
         <v>366</v>
       </c>
@@ -24286,7 +24321,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="792" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A792" s="7" t="s">
         <v>366</v>
       </c>
@@ -24309,7 +24344,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="793" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A793" s="7" t="s">
         <v>70</v>
       </c>
@@ -24338,7 +24373,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="794" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A794" s="7" t="s">
         <v>366</v>
       </c>
@@ -24355,7 +24390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="795" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A795" s="7" t="s">
         <v>70</v>
       </c>
@@ -24381,7 +24416,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="796" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A796" s="7" t="s">
         <v>70</v>
       </c>
@@ -24407,7 +24442,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="797" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A797" s="7" t="s">
         <v>43</v>
       </c>
@@ -24433,7 +24468,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="798" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A798" s="7" t="s">
         <v>70</v>
       </c>
@@ -24462,7 +24497,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="799" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A799" s="7" t="s">
         <v>366</v>
       </c>
@@ -24491,7 +24526,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="800" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A800" s="7" t="s">
         <v>51</v>
       </c>
@@ -24511,7 +24546,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="801" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A801" s="7" t="s">
         <v>51</v>
       </c>
@@ -24531,7 +24566,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="802" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A802" s="7" t="s">
         <v>366</v>
       </c>
@@ -24554,7 +24589,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="803" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A803" s="7" t="s">
         <v>70</v>
       </c>
@@ -24583,7 +24618,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="804" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A804" s="7" t="s">
         <v>366</v>
       </c>
@@ -24603,7 +24638,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="805" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A805" s="7" t="s">
         <v>70</v>
       </c>
@@ -24635,7 +24670,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="806" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A806" s="7" t="s">
         <v>51</v>
       </c>
@@ -24655,7 +24690,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="807" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A807" s="7" t="s">
         <v>51</v>
       </c>
@@ -24675,7 +24710,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="808" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A808" s="7" t="s">
         <v>70</v>
       </c>
@@ -24704,7 +24739,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="809" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A809" s="7" t="s">
         <v>70</v>
       </c>
@@ -24736,7 +24771,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="810" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A810" s="7" t="s">
         <v>70</v>
       </c>
@@ -24765,7 +24800,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="811" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A811" s="7" t="s">
         <v>51</v>
       </c>
@@ -24785,7 +24820,7 @@
         <v>45309</v>
       </c>
     </row>
-    <row r="812" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A812" s="7" t="s">
         <v>366</v>
       </c>
@@ -24805,7 +24840,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="813" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A813" s="7" t="s">
         <v>51</v>
       </c>
@@ -24825,7 +24860,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="814" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A814" s="7" t="s">
         <v>366</v>
       </c>
@@ -24842,7 +24877,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="815" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A815" s="7" t="s">
         <v>70</v>
       </c>
@@ -24874,7 +24909,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="816" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A816" s="7" t="s">
         <v>70</v>
       </c>
@@ -24900,7 +24935,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="817" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A817" s="7" t="s">
         <v>70</v>
       </c>
@@ -24929,7 +24964,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="818" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A818" s="7" t="s">
         <v>70</v>
       </c>
@@ -24958,7 +24993,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="819" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A819" s="7" t="s">
         <v>43</v>
       </c>
@@ -24975,7 +25010,7 @@
         <v>45324</v>
       </c>
     </row>
-    <row r="820" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A820" s="7" t="s">
         <v>70</v>
       </c>
@@ -25007,7 +25042,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="821" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A821" s="7" t="s">
         <v>70</v>
       </c>
@@ -25082,7 +25117,7 @@
         <v>45329</v>
       </c>
     </row>
-    <row r="824" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A824" s="7" t="s">
         <v>366</v>
       </c>
@@ -25096,7 +25131,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="825" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A825" s="7" t="s">
         <v>366</v>
       </c>
@@ -25107,7 +25142,7 @@
         <v>45337</v>
       </c>
     </row>
-    <row r="826" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A826" s="7" t="s">
         <v>51</v>
       </c>
@@ -25147,7 +25182,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="828" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A828" s="7" t="s">
         <v>70</v>
       </c>
@@ -25176,7 +25211,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="829" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A829" s="7" t="s">
         <v>366</v>
       </c>
@@ -25196,7 +25231,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="830" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A830" s="7" t="s">
         <v>366</v>
       </c>
@@ -25213,7 +25248,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="831" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A831" s="7" t="s">
         <v>70</v>
       </c>
@@ -25239,7 +25274,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="832" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A832" s="7" t="s">
         <v>70</v>
       </c>
@@ -25262,7 +25297,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="833" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A833" s="7" t="s">
         <v>366</v>
       </c>
@@ -25282,7 +25317,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="834" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A834" s="7" t="s">
         <v>43</v>
       </c>
@@ -25302,7 +25337,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="835" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A835" s="7" t="s">
         <v>51</v>
       </c>
@@ -25322,7 +25357,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="836" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A836" s="7" t="s">
         <v>70</v>
       </c>
@@ -25351,7 +25386,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="837" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A837" s="7" t="s">
         <v>366</v>
       </c>
@@ -25374,7 +25409,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="838" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A838" s="7" t="s">
         <v>70</v>
       </c>
@@ -25403,7 +25438,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="839" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A839" s="7" t="s">
         <v>51</v>
       </c>
@@ -25483,7 +25518,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="843" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A843" s="7" t="s">
         <v>51</v>
       </c>
@@ -25555,7 +25590,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="846" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A846" s="7" t="s">
         <v>51</v>
       </c>
@@ -25627,7 +25662,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="849" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A849" s="7" t="s">
         <v>366</v>
       </c>
@@ -25644,7 +25679,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="850" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A850" s="7" t="s">
         <v>43</v>
       </c>
@@ -25661,7 +25696,7 @@
         <v>45379</v>
       </c>
     </row>
-    <row r="851" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A851" s="7" t="s">
         <v>51</v>
       </c>
@@ -25965,7 +26000,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="865" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A865" s="7" t="s">
         <v>70</v>
       </c>
@@ -26000,7 +26035,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="866" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A866" s="7" t="s">
         <v>70</v>
       </c>
@@ -26029,7 +26064,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="867" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A867" s="7" t="s">
         <v>70</v>
       </c>
@@ -26055,7 +26090,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="868" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A868" s="7" t="s">
         <v>70</v>
       </c>
@@ -26104,7 +26139,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="870" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A870" s="7" t="s">
         <v>51</v>
       </c>
@@ -26230,7 +26265,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="876" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A876" s="7" t="s">
         <v>51</v>
       </c>
@@ -26270,7 +26305,7 @@
         <v>45437</v>
       </c>
     </row>
-    <row r="878" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A878" s="7" t="s">
         <v>51</v>
       </c>
@@ -26373,7 +26408,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="883" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A883" s="7" t="s">
         <v>43</v>
       </c>
@@ -26399,7 +26434,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="884" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A884" s="7" t="s">
         <v>51</v>
       </c>
@@ -26504,7 +26539,7 @@
         <v>45455</v>
       </c>
     </row>
-    <row r="889" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A889" s="7" t="s">
         <v>51</v>
       </c>
@@ -26604,7 +26639,7 @@
         <v>45466</v>
       </c>
     </row>
-    <row r="894" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A894" s="7" t="s">
         <v>51</v>
       </c>
@@ -26621,7 +26656,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="895" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A895" s="7" t="s">
         <v>51</v>
       </c>
@@ -26644,7 +26679,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="896" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A896" s="7" t="s">
         <v>51</v>
       </c>
@@ -26690,7 +26725,7 @@
         <v>45477</v>
       </c>
     </row>
-    <row r="898" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A898" s="7" t="s">
         <v>70</v>
       </c>
@@ -26716,7 +26751,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="899" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A899" s="7" t="s">
         <v>43</v>
       </c>
@@ -26736,7 +26771,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="900" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A900" s="7" t="s">
         <v>762</v>
       </c>
@@ -26756,7 +26791,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="901" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A901" s="7" t="s">
         <v>43</v>
       </c>
@@ -26773,7 +26808,7 @@
         <v>45482</v>
       </c>
     </row>
-    <row r="902" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A902" s="7" t="s">
         <v>43</v>
       </c>
@@ -26790,7 +26825,7 @@
         <v>45484</v>
       </c>
     </row>
-    <row r="903" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A903" s="7" t="s">
         <v>932</v>
       </c>
@@ -26807,7 +26842,7 @@
         <v>45487</v>
       </c>
     </row>
-    <row r="904" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A904" s="7" t="s">
         <v>43</v>
       </c>
@@ -26830,7 +26865,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="905" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A905" s="7" t="s">
         <v>51</v>
       </c>
@@ -26847,7 +26882,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="906" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A906" s="7" t="s">
         <v>51</v>
       </c>
@@ -26876,7 +26911,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="907" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A907" s="7" t="s">
         <v>43</v>
       </c>
@@ -26899,7 +26934,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="908" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A908" s="7" t="s">
         <v>51</v>
       </c>
@@ -26931,7 +26966,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="909" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A909" s="7" t="s">
         <v>43</v>
       </c>
@@ -27006,7 +27041,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="912" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A912" s="7" t="s">
         <v>43</v>
       </c>
@@ -27026,7 +27061,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="913" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A913" s="7" t="s">
         <v>932</v>
       </c>
@@ -27075,7 +27110,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="915" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A915" s="7" t="s">
         <v>51</v>
       </c>
@@ -27107,7 +27142,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="916" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A916" s="7" t="s">
         <v>43</v>
       </c>
@@ -27190,7 +27225,7 @@
         <v>45509</v>
       </c>
     </row>
-    <row r="920" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A920" s="7" t="s">
         <v>43</v>
       </c>
@@ -27213,7 +27248,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="921" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A921" s="7" t="s">
         <v>43</v>
       </c>
@@ -27236,7 +27271,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="922" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A922" s="7" t="s">
         <v>43</v>
       </c>
@@ -27282,7 +27317,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="924" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A924" s="7" t="s">
         <v>43</v>
       </c>
@@ -27302,7 +27337,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="925" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A925" s="7" t="s">
         <v>51</v>
       </c>
@@ -27337,7 +27372,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="926" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A926" s="7" t="s">
         <v>51</v>
       </c>
@@ -27366,7 +27401,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="927" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A927" s="7" t="s">
         <v>51</v>
       </c>
@@ -27395,7 +27430,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="928" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A928" s="7" t="s">
         <v>224</v>
       </c>
@@ -27415,7 +27450,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="929" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A929" s="7" t="s">
         <v>43</v>
       </c>
@@ -27435,7 +27470,7 @@
         <v>45528</v>
       </c>
     </row>
-    <row r="930" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A930" s="7" t="s">
         <v>51</v>
       </c>
@@ -27455,7 +27490,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="931" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A931" s="7" t="s">
         <v>51</v>
       </c>
@@ -27501,7 +27536,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="933" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A933" s="7" t="s">
         <v>51</v>
       </c>
@@ -27527,7 +27562,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="934" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A934" s="7" t="s">
         <v>51</v>
       </c>
@@ -27547,7 +27582,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="935" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A935" s="7" t="s">
         <v>43</v>
       </c>
@@ -27674,7 +27709,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="940" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A940" s="7" t="s">
         <v>51</v>
       </c>
@@ -27823,7 +27858,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="946" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A946" s="7" t="s">
         <v>51</v>
       </c>
@@ -27855,7 +27890,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="947" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A947" s="7" t="s">
         <v>51</v>
       </c>
@@ -27887,7 +27922,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="948" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A948" s="7" t="s">
         <v>51</v>
       </c>
@@ -27907,7 +27942,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="949" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A949" s="7" t="s">
         <v>51</v>
       </c>
@@ -27930,7 +27965,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="950" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A950" s="7" t="s">
         <v>51</v>
       </c>
@@ -28005,7 +28040,7 @@
         <v>45553</v>
       </c>
     </row>
-    <row r="953" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A953" s="7" t="s">
         <v>51</v>
       </c>
@@ -28040,7 +28075,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="954" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A954" s="7" t="s">
         <v>51</v>
       </c>
@@ -28066,7 +28101,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="955" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A955" s="7" t="s">
         <v>51</v>
       </c>
@@ -28127,7 +28162,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="957" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A957" s="7" t="s">
         <v>51</v>
       </c>
@@ -28147,7 +28182,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="958" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A958" s="7" t="s">
         <v>51</v>
       </c>
@@ -28179,7 +28214,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="959" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A959" s="7" t="s">
         <v>51</v>
       </c>
@@ -28214,7 +28249,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="960" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A960" s="7" t="s">
         <v>51</v>
       </c>
@@ -28237,7 +28272,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="961" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A961" s="7" t="s">
         <v>51</v>
       </c>
@@ -28272,7 +28307,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="962" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A962" s="7" t="s">
         <v>51</v>
       </c>
@@ -28301,7 +28336,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="963" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A963" s="7" t="s">
         <v>43</v>
       </c>
@@ -28384,7 +28419,7 @@
         <v>45586</v>
       </c>
     </row>
-    <row r="967" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A967" s="7" t="s">
         <v>51</v>
       </c>
@@ -28416,7 +28451,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="968" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A968" s="7" t="s">
         <v>51</v>
       </c>
@@ -28488,7 +28523,7 @@
         <v>45590</v>
       </c>
     </row>
-    <row r="971" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A971" s="7" t="s">
         <v>51</v>
       </c>
@@ -28606,7 +28641,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="976" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A976" s="7" t="s">
         <v>51</v>
       </c>
@@ -28632,7 +28667,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="977" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A977" s="7" t="s">
         <v>51</v>
       </c>
@@ -28667,7 +28702,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="978" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A978" s="7" t="s">
         <v>51</v>
       </c>
@@ -28696,7 +28731,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="979" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A979" s="7" t="s">
         <v>51</v>
       </c>
@@ -28803,7 +28838,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="983" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A983" s="7" t="s">
         <v>51</v>
       </c>
@@ -28835,7 +28870,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="984" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A984" s="7" t="s">
         <v>43</v>
       </c>
@@ -28855,7 +28890,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="985" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A985" s="7" t="s">
         <v>51</v>
       </c>
@@ -28890,7 +28925,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="986" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A986" s="7" t="s">
         <v>51</v>
       </c>
@@ -28922,7 +28957,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="987" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A987" s="7" t="s">
         <v>51</v>
       </c>
@@ -28954,7 +28989,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="988" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A988" s="7" t="s">
         <v>70</v>
       </c>
@@ -28980,7 +29015,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="989" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A989" s="7" t="s">
         <v>51</v>
       </c>
@@ -29009,7 +29044,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="990" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A990" s="7" t="s">
         <v>51</v>
       </c>
@@ -29041,7 +29076,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="991" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A991" s="7" t="s">
         <v>51</v>
       </c>
@@ -29076,7 +29111,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="992" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A992" s="7" t="s">
         <v>51</v>
       </c>
@@ -29105,7 +29140,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="993" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A993" s="7" t="s">
         <v>366</v>
       </c>
@@ -29125,7 +29160,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="994" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A994" s="7" t="s">
         <v>51</v>
       </c>
@@ -29139,7 +29174,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="995" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A995" s="7" t="s">
         <v>51</v>
       </c>
@@ -29153,7 +29188,7 @@
         <v>45630</v>
       </c>
     </row>
-    <row r="996" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A996" s="7" t="s">
         <v>51</v>
       </c>
@@ -29188,7 +29223,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="997" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A997" s="7" t="s">
         <v>366</v>
       </c>
@@ -29211,7 +29246,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="998" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A998" s="7" t="s">
         <v>51</v>
       </c>
@@ -29243,7 +29278,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="999" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A999" s="7" t="s">
         <v>70</v>
       </c>
@@ -29272,7 +29307,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1000" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1000" s="7" t="s">
         <v>366</v>
       </c>
@@ -29292,7 +29327,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1001" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1001" s="7" t="s">
         <v>70</v>
       </c>
@@ -29318,7 +29353,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1002" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1002" s="7" t="s">
         <v>51</v>
       </c>
@@ -29350,7 +29385,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1003" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1003" s="7" t="s">
         <v>366</v>
       </c>
@@ -29382,7 +29417,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="1004" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1004" s="7" t="s">
         <v>51</v>
       </c>
@@ -29414,7 +29449,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1005" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1005" s="7" t="s">
         <v>366</v>
       </c>
@@ -29437,7 +29472,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1006" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1006" s="7" t="s">
         <v>366</v>
       </c>
@@ -29460,7 +29495,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1007" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1007" s="7" t="s">
         <v>366</v>
       </c>
@@ -29483,7 +29518,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1008" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1008" s="7" t="s">
         <v>70</v>
       </c>
@@ -29509,7 +29544,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1009" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1009" s="7" t="s">
         <v>51</v>
       </c>
@@ -29541,7 +29576,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1010" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1010" s="7" t="s">
         <v>70</v>
       </c>
@@ -29567,7 +29602,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1011" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1011" s="7" t="s">
         <v>70</v>
       </c>
@@ -29593,7 +29628,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1012" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1012" s="7" t="s">
         <v>70</v>
       </c>
@@ -29625,7 +29660,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1013" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1013" s="7" t="s">
         <v>366</v>
       </c>
@@ -29654,7 +29689,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="1014" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1014" s="7" t="s">
         <v>70</v>
       </c>
@@ -29683,7 +29718,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1015" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1015" s="7" t="s">
         <v>70</v>
       </c>
@@ -29709,7 +29744,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1016" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1016" s="7" t="s">
         <v>70</v>
       </c>
@@ -29735,7 +29770,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1017" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1017" s="7" t="s">
         <v>366</v>
       </c>
@@ -29755,7 +29790,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1018" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1018" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1018" s="7" t="s">
         <v>70</v>
       </c>
@@ -29781,7 +29816,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1019" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1019" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1019" s="7" t="s">
         <v>51</v>
       </c>
@@ -29801,7 +29836,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1020" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1020" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1020" s="7" t="s">
         <v>51</v>
       </c>
@@ -29827,7 +29862,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1021" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1021" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1021" s="7" t="s">
         <v>70</v>
       </c>
@@ -29859,7 +29894,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="1022" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1022" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1022" s="7" t="s">
         <v>70</v>
       </c>
@@ -29888,7 +29923,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1023" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1023" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1023" s="7" t="s">
         <v>70</v>
       </c>
@@ -29917,7 +29952,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1024" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1024" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1024" s="7" t="s">
         <v>366</v>
       </c>
@@ -29943,7 +29978,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1025" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1025" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1025" s="7" t="s">
         <v>366</v>
       </c>
@@ -29963,7 +29998,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1026" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1026" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1026" s="7" t="s">
         <v>1080</v>
       </c>
@@ -29995,7 +30030,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1027" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1027" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1027" s="7" t="s">
         <v>1080</v>
       </c>
@@ -30024,7 +30059,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1028" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1028" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1028" s="7" t="s">
         <v>70</v>
       </c>
@@ -30050,7 +30085,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1029" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1029" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1029" s="7" t="s">
         <v>70</v>
       </c>
@@ -30079,7 +30114,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="1030" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1030" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1030" s="7" t="s">
         <v>70</v>
       </c>
@@ -30105,7 +30140,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1031" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1031" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1031" s="7" t="s">
         <v>70</v>
       </c>
@@ -30134,7 +30169,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="1032" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1032" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1032" s="7" t="s">
         <v>366</v>
       </c>
@@ -30151,7 +30186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1033" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1033" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1033" s="7" t="s">
         <v>70</v>
       </c>
@@ -30183,7 +30218,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="1034" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1034" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1034" s="7" t="s">
         <v>1080</v>
       </c>
@@ -30215,7 +30250,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1035" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1035" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1035" s="7" t="s">
         <v>366</v>
       </c>
@@ -30232,7 +30267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1036" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1036" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1036" s="7" t="s">
         <v>70</v>
       </c>
@@ -30266,7 +30301,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1037" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1037" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1037" s="7" t="s">
         <v>366</v>
       </c>
@@ -30289,7 +30324,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1038" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1038" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1038" s="7" t="s">
         <v>51</v>
       </c>
@@ -30309,7 +30344,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="1039" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1039" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1039" s="7" t="s">
         <v>1080</v>
       </c>
@@ -30338,7 +30373,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1040" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1040" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1040" s="7" t="s">
         <v>366</v>
       </c>
@@ -30361,7 +30396,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1041" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1041" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1041" s="7" t="s">
         <v>366</v>
       </c>
@@ -30387,7 +30422,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1042" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1042" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1042" s="7" t="s">
         <v>1080</v>
       </c>
@@ -30416,7 +30451,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1043" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1043" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1043" s="7" t="s">
         <v>70</v>
       </c>
@@ -30442,7 +30477,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1044" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1044" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1044" s="7" t="s">
         <v>70</v>
       </c>
@@ -30471,7 +30506,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="1045" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1045" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1045" s="7" t="s">
         <v>1080</v>
       </c>
@@ -30503,7 +30538,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1046" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1046" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1046" s="7" t="s">
         <v>70</v>
       </c>
@@ -30532,7 +30567,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1047" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1047" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1047" s="7" t="s">
         <v>1080</v>
       </c>
@@ -30561,7 +30596,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1048" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1048" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1048" s="7" t="s">
         <v>366</v>
       </c>
@@ -30590,7 +30625,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="1049" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1049" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1049" s="7" t="s">
         <v>70</v>
       </c>
@@ -30619,7 +30654,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="1050" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1050" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1050" s="7" t="s">
         <v>70</v>
       </c>
@@ -30648,7 +30683,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="1051" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1051" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1051" s="7" t="s">
         <v>366</v>
       </c>
@@ -30665,7 +30700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1052" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1052" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1052" s="7" t="s">
         <v>366</v>
       </c>
@@ -30682,7 +30717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1053" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1053" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1053" s="7" t="s">
         <v>70</v>
       </c>
@@ -30716,7 +30751,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1054" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1054" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1054" s="7" t="s">
         <v>366</v>
       </c>
@@ -30742,7 +30777,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1055" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1055" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1055" s="7" t="s">
         <v>366</v>
       </c>
@@ -30765,7 +30800,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="1056" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1056" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1056" s="7" t="s">
         <v>51</v>
       </c>
@@ -30791,7 +30826,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="1057" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1057" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1057" s="7" t="s">
         <v>51</v>
       </c>
@@ -30817,7 +30852,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="1058" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1058" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1058" s="7" t="s">
         <v>51</v>
       </c>
@@ -30852,7 +30887,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1059" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1059" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1059" s="7" t="s">
         <v>366</v>
       </c>
@@ -30872,7 +30907,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1060" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1060" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1060" s="7" t="s">
         <v>70</v>
       </c>
@@ -30898,7 +30933,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1061" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1061" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1061" s="7" t="s">
         <v>70</v>
       </c>
@@ -30924,7 +30959,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1062" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1062" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1062" s="7" t="s">
         <v>366</v>
       </c>
@@ -31036,7 +31071,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="1067" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1067" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1067" s="7" t="s">
         <v>366</v>
       </c>
@@ -31053,7 +31088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1068" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1068" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1068" s="7" t="s">
         <v>51</v>
       </c>
@@ -31085,7 +31120,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1069" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1069" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1069" s="7" t="s">
         <v>51</v>
       </c>
@@ -31117,7 +31152,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="1070" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1070" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1070" s="7" t="s">
         <v>51</v>
       </c>
@@ -31149,7 +31184,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="1071" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1071" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1071" s="7" t="s">
         <v>51</v>
       </c>
@@ -31178,7 +31213,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="1072" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1072" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1072" s="7" t="s">
         <v>51</v>
       </c>
@@ -31204,7 +31239,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="1073" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1073" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1073" s="7" t="s">
         <v>70</v>
       </c>
@@ -31230,7 +31265,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1074" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1074" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1074" s="7" t="s">
         <v>51</v>
       </c>
@@ -31259,7 +31294,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1075" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1075" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1075" s="7" t="s">
         <v>51</v>
       </c>
@@ -31296,7 +31331,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1076" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1076" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1076" s="7" t="s">
         <v>51</v>
       </c>
@@ -31319,7 +31354,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1077" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1077" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1077" s="7" t="s">
         <v>70</v>
       </c>
@@ -31368,7 +31403,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="1079" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1079" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1079" s="7" t="s">
         <v>70</v>
       </c>
@@ -31394,7 +31429,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1080" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1080" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1080" s="7" t="s">
         <v>51</v>
       </c>
@@ -31423,7 +31458,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1081" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1081" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1081" s="7" t="s">
         <v>51</v>
       </c>
@@ -31452,7 +31487,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1082" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1082" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1082" s="7" t="s">
         <v>51</v>
       </c>
@@ -31527,7 +31562,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="1085" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1085" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1085" s="7" t="s">
         <v>51</v>
       </c>
@@ -31556,7 +31591,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1086" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1086" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1086" s="7" t="s">
         <v>51</v>
       </c>
@@ -31588,7 +31623,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1087" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1087" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1087" s="7" t="s">
         <v>51</v>
       </c>
@@ -31640,7 +31675,7 @@
         <v>45773</v>
       </c>
     </row>
-    <row r="1089" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1089" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1089" s="7" t="s">
         <v>51</v>
       </c>
@@ -31721,7 +31756,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1092" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1092" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1092" s="7" t="s">
         <v>70</v>
       </c>
@@ -31747,7 +31782,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1093" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1093" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1093" s="7" t="s">
         <v>51</v>
       </c>
@@ -31785,7 +31820,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1094" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1094" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1094" s="7" t="s">
         <v>51</v>
       </c>
@@ -31883,7 +31918,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1098" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1098" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1098" s="7" t="s">
         <v>70</v>
       </c>
@@ -31993,7 +32028,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="1102" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1102" s="7" t="s">
         <v>51</v>
       </c>
@@ -32019,7 +32054,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="1103" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1103" s="7" t="s">
         <v>51</v>
       </c>
@@ -32048,7 +32083,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="1104" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1104" s="7" t="s">
         <v>51</v>
       </c>
@@ -32281,7 +32316,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="1114" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1114" s="7" t="s">
         <v>51</v>
       </c>
@@ -32361,7 +32396,7 @@
         <v>45815</v>
       </c>
     </row>
-    <row r="1117" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1117" s="7" t="s">
         <v>1431</v>
       </c>
@@ -32381,7 +32416,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="1118" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1118" s="7" t="s">
         <v>1431</v>
       </c>
@@ -32401,7 +32436,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="1119" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1119" s="7" t="s">
         <v>1431</v>
       </c>
@@ -32421,7 +32456,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="1120" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1120" s="7" t="s">
         <v>1431</v>
       </c>
@@ -32478,7 +32513,7 @@
         <v>45820</v>
       </c>
     </row>
-    <row r="1123" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1123" s="7" t="s">
         <v>51</v>
       </c>
@@ -32498,7 +32533,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="1124" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1124" s="7" t="s">
         <v>51</v>
       </c>
@@ -32518,7 +32553,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="1125" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1125" s="7" t="s">
         <v>51</v>
       </c>
@@ -32550,7 +32585,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1126" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1126" s="7" t="s">
         <v>1431</v>
       </c>
@@ -32850,7 +32885,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="1139" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1139" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1139" s="7" t="s">
         <v>1431</v>
       </c>
@@ -32870,7 +32905,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="1140" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1140" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1140" s="7" t="s">
         <v>1431</v>
       </c>
@@ -32890,7 +32925,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="1141" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1141" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1141" s="7" t="s">
         <v>51</v>
       </c>
@@ -33244,7 +33279,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="1157" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1157" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1157" s="7" t="s">
         <v>43</v>
       </c>
@@ -33371,7 +33406,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1162" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1162" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1162" s="7" t="s">
         <v>43</v>
       </c>
@@ -33391,7 +33426,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1163" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1163" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1163" s="7" t="s">
         <v>1431</v>
       </c>
@@ -33411,7 +33446,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="1164" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1164" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1164" s="7" t="s">
         <v>1431</v>
       </c>
@@ -33454,7 +33489,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="1166" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1166" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1166" s="7" t="s">
         <v>51</v>
       </c>
@@ -33477,7 +33512,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1167" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1167" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1167" s="7" t="s">
         <v>51</v>
       </c>
@@ -33512,7 +33547,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1168" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1168" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1168" s="7" t="s">
         <v>51</v>
       </c>
@@ -33556,7 +33591,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1169" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1169" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1169" s="7" t="s">
         <v>51</v>
       </c>
@@ -33677,7 +33712,7 @@
         <v>45869</v>
       </c>
     </row>
-    <row r="1174" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1174" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1174" s="7" t="s">
         <v>51</v>
       </c>
@@ -33712,7 +33747,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1175" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1175" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1175" s="7" t="s">
         <v>51</v>
       </c>
@@ -33744,7 +33779,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1176" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1176" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1176" s="7" t="s">
         <v>43</v>
       </c>
@@ -33764,7 +33799,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1177" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1177" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1177" s="7" t="s">
         <v>43</v>
       </c>
@@ -33790,7 +33825,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1178" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1178" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1178" s="7" t="s">
         <v>51</v>
       </c>
@@ -33942,7 +33977,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="1184" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1184" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1184" s="7" t="s">
         <v>1431</v>
       </c>
@@ -34041,7 +34076,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="1188" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1188" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1188" s="7" t="s">
         <v>1431</v>
       </c>
@@ -34110,7 +34145,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="1191" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1191" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1191" s="7" t="s">
         <v>51</v>
       </c>
@@ -34162,7 +34197,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="1193" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1193" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1193" s="7" t="s">
         <v>51</v>
       </c>
@@ -34240,7 +34275,7 @@
         <v>45897</v>
       </c>
     </row>
-    <row r="1196" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1196" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1196" s="7" t="s">
         <v>51</v>
       </c>
@@ -34272,7 +34307,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="1197" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1197" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1197" s="7" t="s">
         <v>43</v>
       </c>
@@ -34301,7 +34336,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1198" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1198" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1198" s="7" t="s">
         <v>51</v>
       </c>
@@ -34330,7 +34365,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="1199" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1199" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1199" s="7" t="s">
         <v>1431</v>
       </c>
@@ -34422,7 +34457,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="1203" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1203" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1203" s="7" t="s">
         <v>51</v>
       </c>
@@ -34454,7 +34489,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="1204" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1204" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1204" s="7" t="s">
         <v>51</v>
       </c>
@@ -34480,7 +34515,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="1205" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1205" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1205" s="7" t="s">
         <v>1431</v>
       </c>
@@ -34500,7 +34535,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="1206" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1206" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1206" s="7" t="s">
         <v>51</v>
       </c>
@@ -34535,7 +34570,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1207" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1207" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1207" s="7" t="s">
         <v>51</v>
       </c>
@@ -34677,7 +34712,7 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="1213" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1213" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1213" s="7" t="s">
         <v>51</v>
       </c>
@@ -34706,7 +34741,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1214" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1214" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1214" s="7" t="s">
         <v>51</v>
       </c>
@@ -34738,7 +34773,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1215" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1215" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1215" s="7" t="s">
         <v>1431</v>
       </c>
@@ -34758,7 +34793,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="1216" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1216" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1216" s="7" t="s">
         <v>51</v>
       </c>
@@ -34793,7 +34828,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1217" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1217" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1217" s="7" t="s">
         <v>51</v>
       </c>
@@ -34825,7 +34860,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1218" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1218" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1218" s="7" t="s">
         <v>1431</v>
       </c>
@@ -34845,7 +34880,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="1219" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1219" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1219" s="7" t="s">
         <v>51</v>
       </c>
@@ -34926,7 +34961,7 @@
         <v>45932</v>
       </c>
     </row>
-    <row r="1222" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1222" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1222" s="7" t="s">
         <v>51</v>
       </c>
@@ -34955,7 +34990,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1223" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1223" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1223" s="7" t="s">
         <v>51</v>
       </c>
@@ -34981,7 +35016,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1224" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1224" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1224" s="7" t="s">
         <v>51</v>
       </c>
@@ -35016,7 +35051,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1225" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1225" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1225" s="7" t="s">
         <v>43</v>
       </c>
@@ -35036,7 +35071,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="1226" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1226" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1226" s="7" t="s">
         <v>43</v>
       </c>
@@ -35206,7 +35241,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="1234" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1234" s="7" t="s">
         <v>51</v>
       </c>
@@ -35241,7 +35276,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1235" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1235" s="7" t="s">
         <v>51</v>
       </c>
@@ -35273,7 +35308,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1236" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1236" s="7" t="s">
         <v>51</v>
       </c>
@@ -35308,7 +35343,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1237" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1237" s="7" t="s">
         <v>51</v>
       </c>
@@ -35343,7 +35378,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1238" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1238" s="7" t="s">
         <v>51</v>
       </c>
@@ -35378,7 +35413,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1239" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1239" s="7" t="s">
         <v>51</v>
       </c>
@@ -35410,7 +35445,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1240" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1240" s="7" t="s">
         <v>51</v>
       </c>
@@ -35439,7 +35474,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="1241" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1241" s="7" t="s">
         <v>51</v>
       </c>
@@ -35508,7 +35543,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="1244" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1244" s="7" t="s">
         <v>51</v>
       </c>
@@ -35540,7 +35575,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1245" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1245" s="7" t="s">
         <v>51</v>
       </c>
@@ -35566,7 +35601,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1246" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1246" s="7" t="s">
         <v>51</v>
       </c>
@@ -35909,7 +35944,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="1260" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1260" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1260" s="7" t="s">
         <v>70</v>
       </c>
@@ -35947,7 +35982,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="1261" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1261" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1261" s="7" t="s">
         <v>70</v>
       </c>
@@ -35979,7 +36014,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="1262" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1262" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1262" s="7" t="s">
         <v>70</v>
       </c>
@@ -36014,7 +36049,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1263" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1263" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1263" s="7" t="s">
         <v>70</v>
       </c>
@@ -36043,7 +36078,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1264" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1264" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1264" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36075,7 +36110,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1265" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1265" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1265" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36107,7 +36142,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1266" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1266" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1266" s="7" t="s">
         <v>70</v>
       </c>
@@ -36141,7 +36176,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1267" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1267" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1267" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36173,7 +36208,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1268" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1268" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1268" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36202,7 +36237,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1269" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1269" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1269" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36231,7 +36266,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1270" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1270" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1270" s="7" t="s">
         <v>70</v>
       </c>
@@ -36265,7 +36300,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1271" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1271" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1271" s="7" t="s">
         <v>366</v>
       </c>
@@ -36288,7 +36323,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1272" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1272" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1272" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36320,7 +36355,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1273" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1273" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1273" s="7" t="s">
         <v>366</v>
       </c>
@@ -36340,7 +36375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1274" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1274" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1274" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36366,7 +36401,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1275" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1275" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1275" s="7" t="s">
         <v>366</v>
       </c>
@@ -36386,7 +36421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1276" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1276" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1276" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36415,7 +36450,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1277" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1277" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1277" s="7" t="s">
         <v>51</v>
       </c>
@@ -36450,7 +36485,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1278" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1278" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1278" s="7" t="s">
         <v>366</v>
       </c>
@@ -36470,7 +36505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1279" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1279" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1279" s="7" t="s">
         <v>51</v>
       </c>
@@ -36502,7 +36537,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1280" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1280" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1280" s="7" t="s">
         <v>366</v>
       </c>
@@ -36522,7 +36557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1281" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1281" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1281" s="7" t="s">
         <v>366</v>
       </c>
@@ -36554,7 +36589,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="1282" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1282" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1282" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36583,7 +36618,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1283" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1283" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1283" s="7" t="s">
         <v>51</v>
       </c>
@@ -36618,7 +36653,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1284" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1284" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1284" s="7" t="s">
         <v>366</v>
       </c>
@@ -36644,7 +36679,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1285" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1285" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1285" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36673,7 +36708,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1286" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1286" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1286" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36705,7 +36740,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1287" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1287" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1287" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36737,7 +36772,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1288" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1288" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1288" s="7" t="s">
         <v>366</v>
       </c>
@@ -36763,7 +36798,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1289" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1289" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1289" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36792,7 +36827,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1290" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1290" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1290" s="7" t="s">
         <v>366</v>
       </c>
@@ -36812,7 +36847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1291" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1291" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1291" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36844,7 +36879,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1292" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1292" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1292" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36876,7 +36911,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1293" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1293" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1293" s="7" t="s">
         <v>366</v>
       </c>
@@ -36893,7 +36928,7 @@
         <v>3647</v>
       </c>
     </row>
-    <row r="1294" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1294" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1294" s="7" t="s">
         <v>1080</v>
       </c>
@@ -36925,7 +36960,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1295" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1295" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1295" s="7" t="s">
         <v>366</v>
       </c>
@@ -36942,7 +36977,7 @@
         <v>3494</v>
       </c>
     </row>
-    <row r="1296" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1296" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1296" s="7" t="s">
         <v>51</v>
       </c>
@@ -36977,7 +37012,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1297" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1297" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1297" s="7" t="s">
         <v>366</v>
       </c>
@@ -37000,7 +37035,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1298" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1298" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1298" s="7" t="s">
         <v>70</v>
       </c>
@@ -37029,7 +37064,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1299" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1299" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1299" s="7" t="s">
         <v>366</v>
       </c>
@@ -37046,7 +37081,7 @@
         <v>4789</v>
       </c>
     </row>
-    <row r="1300" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1300" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1300" s="7" t="s">
         <v>1080</v>
       </c>
@@ -37075,7 +37110,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1301" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1301" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1301" s="7" t="s">
         <v>366</v>
       </c>
@@ -37095,7 +37130,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1302" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1302" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1302" s="7" t="s">
         <v>1080</v>
       </c>
@@ -37124,7 +37159,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1303" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1303" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1303" s="7" t="s">
         <v>1080</v>
       </c>
@@ -37156,7 +37191,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1304" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1304" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1304" s="7" t="s">
         <v>366</v>
       </c>
@@ -37173,7 +37208,7 @@
         <v>4789</v>
       </c>
     </row>
-    <row r="1305" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1305" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1305" s="7" t="s">
         <v>51</v>
       </c>
@@ -37208,7 +37243,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1306" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1306" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1306" s="7" t="s">
         <v>366</v>
       </c>
@@ -37228,7 +37263,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1307" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1307" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1307" s="7" t="s">
         <v>1080</v>
       </c>
@@ -37257,7 +37292,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1308" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1308" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1308" s="7" t="s">
         <v>51</v>
       </c>
@@ -37292,7 +37327,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1309" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1309" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1309" s="7" t="s">
         <v>1080</v>
       </c>
@@ -37321,7 +37356,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1310" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1310" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1310" s="7" t="s">
         <v>1080</v>
       </c>
@@ -37353,7 +37388,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1311" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1311" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1311" s="7" t="s">
         <v>1080</v>
       </c>
@@ -37385,7 +37420,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1312" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1312" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1312" s="7" t="s">
         <v>70</v>
       </c>
@@ -37422,7 +37457,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1313" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1313" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1313" s="7" t="s">
         <v>70</v>
       </c>
@@ -37451,7 +37486,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1314" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1314" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1314" s="7" t="s">
         <v>366</v>
       </c>
@@ -37474,7 +37509,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="1315" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1315" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1315" s="7" t="s">
         <v>51</v>
       </c>
@@ -37509,7 +37544,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1316" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1316" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1316" s="7" t="s">
         <v>1080</v>
       </c>
@@ -37538,7 +37573,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1317" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1317" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1317" s="7" t="s">
         <v>51</v>
       </c>
@@ -37573,7 +37608,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1318" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1318" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1318" s="7" t="s">
         <v>51</v>
       </c>
@@ -37608,7 +37643,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1319" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1319" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1319" s="7" t="s">
         <v>366</v>
       </c>
@@ -37625,7 +37660,7 @@
         <v>3947</v>
       </c>
     </row>
-    <row r="1320" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1320" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1320" s="7" t="s">
         <v>1080</v>
       </c>
@@ -37654,7 +37689,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="1321" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1321" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1321" s="7" t="s">
         <v>366</v>
       </c>
@@ -37677,7 +37712,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="1322" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1322" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1322" s="7" t="s">
         <v>366</v>
       </c>
@@ -37700,7 +37735,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="1323" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1323" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1323" s="7" t="s">
         <v>51</v>
       </c>
@@ -37735,7 +37770,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1324" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1324" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1324" s="7" t="s">
         <v>366</v>
       </c>
@@ -37761,7 +37796,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1325" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1325" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1325" s="7" t="s">
         <v>366</v>
       </c>
@@ -37787,7 +37822,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="1326" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1326" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1326" s="7" t="s">
         <v>1080</v>
       </c>
@@ -37819,7 +37854,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1327" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1327" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1327" s="7" t="s">
         <v>70</v>
       </c>
@@ -37853,7 +37888,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1328" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1328" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1328" s="7" t="s">
         <v>70</v>
       </c>
@@ -37887,7 +37922,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1329" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1329" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1329" s="7" t="s">
         <v>366</v>
       </c>
@@ -37907,7 +37942,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1330" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1330" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1330" s="7" t="s">
         <v>70</v>
       </c>
@@ -37936,7 +37971,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1331" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1331" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1331" s="7" t="s">
         <v>43</v>
       </c>
@@ -37959,7 +37994,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1332" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1332" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1332" s="7" t="s">
         <v>70</v>
       </c>
@@ -37996,7 +38031,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1333" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1333" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1333" s="7" t="s">
         <v>70</v>
       </c>
@@ -38033,7 +38068,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1334" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1334" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1334" s="7" t="s">
         <v>1080</v>
       </c>
@@ -38065,7 +38100,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1335" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1335" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1335" s="7" t="s">
         <v>366</v>
       </c>
@@ -38085,7 +38120,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1336" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1336" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1336" s="7" t="s">
         <v>70</v>
       </c>
@@ -38114,7 +38149,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1337" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1337" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1337" s="7" t="s">
         <v>70</v>
       </c>
@@ -38191,7 +38226,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="1340" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1340" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1340" s="7" t="s">
         <v>366</v>
       </c>
@@ -38212,7 +38247,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1341" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1341" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1341" s="7" t="s">
         <v>366</v>
       </c>
@@ -38232,7 +38267,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1342" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1342" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1342" s="7" t="s">
         <v>1080</v>
       </c>
@@ -38264,7 +38299,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1343" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1343" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1343" s="7" t="s">
         <v>1080</v>
       </c>
@@ -38296,7 +38331,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1344" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1344" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1344" s="7" t="s">
         <v>70</v>
       </c>
@@ -38325,7 +38360,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1345" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1345" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1345" s="7" t="s">
         <v>70</v>
       </c>
@@ -38362,7 +38397,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="1346" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1346" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1346" s="7" t="s">
         <v>366</v>
       </c>
@@ -38385,7 +38420,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="1347" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1347" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1347" s="7" t="s">
         <v>366</v>
       </c>
@@ -38414,7 +38449,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="1348" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1348" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1348" s="7" t="s">
         <v>51</v>
       </c>
@@ -38449,7 +38484,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1349" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1349" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1349" s="7" t="s">
         <v>51</v>
       </c>
@@ -38481,7 +38516,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="1350" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1350" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1350" s="7" t="s">
         <v>51</v>
       </c>
@@ -38510,7 +38545,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="1351" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1351" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1351" s="7" t="s">
         <v>70</v>
       </c>
@@ -38547,7 +38582,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1352" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1352" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1352" s="7" t="s">
         <v>51</v>
       </c>
@@ -38573,7 +38608,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1353" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1353" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1353" s="7" t="s">
         <v>51</v>
       </c>
@@ -38599,7 +38634,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1354" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1354" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1354" s="7" t="s">
         <v>51</v>
       </c>
@@ -38640,7 +38675,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1355" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1355" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1355" s="7" t="s">
         <v>70</v>
       </c>
@@ -38669,7 +38704,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1356" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1356" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1356" s="7" t="s">
         <v>70</v>
       </c>
@@ -38735,7 +38770,7 @@
         <v>46118</v>
       </c>
     </row>
-    <row r="1359" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1359" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1359" s="7" t="s">
         <v>70</v>
       </c>
@@ -38761,7 +38796,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1360" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1360" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1360" s="7" t="s">
         <v>70</v>
       </c>
@@ -38790,7 +38825,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1361" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1361" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1361" s="7" t="s">
         <v>70</v>
       </c>
@@ -38822,7 +38857,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1362" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1362" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1362" s="7" t="s">
         <v>51</v>
       </c>
@@ -38857,7 +38892,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1363" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1363" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1363" s="7" t="s">
         <v>70</v>
       </c>
@@ -38889,7 +38924,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="1364" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1364" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1364" s="7" t="s">
         <v>70</v>
       </c>
@@ -38918,7 +38953,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1365" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1365" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1365" s="7" t="s">
         <v>70</v>
       </c>
@@ -38950,7 +38985,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1366" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1366" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1366" s="7" t="s">
         <v>70</v>
       </c>
@@ -38976,7 +39011,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1367" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1367" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1367" s="7" t="s">
         <v>70</v>
       </c>
@@ -39049,7 +39084,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="1369" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1369" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1369" s="7" t="s">
         <v>70</v>
       </c>
@@ -39084,7 +39119,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="1370" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1370" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1370" s="7" t="s">
         <v>70</v>
       </c>
@@ -39116,7 +39151,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="1371" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1371" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1371" s="7" t="s">
         <v>51</v>
       </c>
@@ -39145,7 +39180,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1372" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1372" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1372" s="7" t="s">
         <v>51</v>
       </c>
@@ -39214,7 +39249,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="1375" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1375" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1375" s="7" t="s">
         <v>51</v>
       </c>
@@ -39246,7 +39281,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="1376" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1376" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1376" s="7" t="s">
         <v>51</v>
       </c>
@@ -39284,7 +39319,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1377" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1377" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1377" s="7" t="s">
         <v>70</v>
       </c>
@@ -39316,7 +39351,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="1378" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1378" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1378" s="7" t="s">
         <v>51</v>
       </c>
@@ -39408,7 +39443,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="1382" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1382" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1382" s="7" t="s">
         <v>70</v>
       </c>
@@ -39437,7 +39472,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="1383" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1383" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1383" s="7" t="s">
         <v>51</v>
       </c>
@@ -39534,7 +39569,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="1387" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1387" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1387" s="7" t="s">
         <v>1431</v>
       </c>
@@ -39554,7 +39589,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="1388" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1388" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1388" s="7" t="s">
         <v>51</v>
       </c>
@@ -39586,7 +39621,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1389" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1389" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1389" s="7" t="s">
         <v>51</v>
       </c>
@@ -39641,7 +39676,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="1391" spans="1:25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1391" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1391" s="7" t="s">
         <v>51</v>
       </c>
@@ -39716,7 +39751,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="1394" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1394" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1394" s="7" t="s">
         <v>51</v>
       </c>
@@ -39791,7 +39826,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="1397" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1397" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1397" s="7" t="s">
         <v>51</v>
       </c>
@@ -39820,7 +39855,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1398" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1398" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1398" s="7" t="s">
         <v>51</v>
       </c>
@@ -39843,7 +39878,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1399" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1399" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1399" s="7" t="s">
         <v>51</v>
       </c>
@@ -39866,7 +39901,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1400" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1400" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1400" s="7" t="s">
         <v>51</v>
       </c>
@@ -40062,7 +40097,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="1408" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1408" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1408" s="7" t="s">
         <v>51</v>
       </c>
@@ -40091,7 +40126,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1409" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1409" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1409" s="7" t="s">
         <v>1429</v>
       </c>
@@ -40211,7 +40246,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="1414" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1414" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1414" s="7" t="s">
         <v>51</v>
       </c>
@@ -40272,7 +40307,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="1416" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1416" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1416" s="7" t="s">
         <v>1431</v>
       </c>
@@ -40292,7 +40327,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="1417" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1417" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1417" s="7" t="s">
         <v>51</v>
       </c>
@@ -40321,7 +40356,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1418" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1418" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1418" s="7" t="s">
         <v>51</v>
       </c>
@@ -40350,7 +40385,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1419" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1419" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1419" s="7" t="s">
         <v>43</v>
       </c>
@@ -40376,7 +40411,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1420" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1420" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1420" s="7" t="s">
         <v>43</v>
       </c>
@@ -40425,7 +40460,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="1422" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1422" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1422" s="7" t="s">
         <v>1431</v>
       </c>
@@ -40445,7 +40480,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="1423" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1423" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1423" s="7" t="s">
         <v>51</v>
       </c>
@@ -40524,7 +40559,7 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="1426" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1426" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1426" s="7" t="s">
         <v>1431</v>
       </c>
@@ -40547,7 +40582,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1427" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1427" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1427" s="7" t="s">
         <v>51</v>
       </c>
@@ -40579,7 +40614,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1428" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1428" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1428" s="7" t="s">
         <v>1431</v>
       </c>
@@ -40715,7 +40750,7 @@
         <v>46215</v>
       </c>
     </row>
-    <row r="1434" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1434" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1434" s="7" t="s">
         <v>51</v>
       </c>
@@ -40747,7 +40782,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1435" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1435" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1435" s="7" t="s">
         <v>51</v>
       </c>
@@ -40782,7 +40817,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1436" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1436" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1436" s="7" t="s">
         <v>1431</v>
       </c>
@@ -40802,7 +40837,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="1437" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1437" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1437" s="7" t="s">
         <v>43</v>
       </c>
@@ -40837,7 +40872,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1438" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1438" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1438" s="7" t="s">
         <v>51</v>
       </c>
@@ -40866,7 +40901,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1439" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1439" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1439" s="7" t="s">
         <v>51</v>
       </c>
@@ -40901,7 +40936,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1440" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1440" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1440" s="7" t="s">
         <v>51</v>
       </c>
@@ -40936,7 +40971,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1441" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1441" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1441" s="7" t="s">
         <v>43</v>
       </c>
@@ -40974,7 +41009,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="1442" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1442" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1442" s="7" t="s">
         <v>51</v>
       </c>
@@ -41049,7 +41084,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="1445" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1445" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1445" s="7" t="s">
         <v>51</v>
       </c>
@@ -41081,14 +41116,320 @@
         <v>949</v>
       </c>
     </row>
+    <row r="1446" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1446" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1446" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1446" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J1446" s="1">
+        <v>46232</v>
+      </c>
+      <c r="K1446" s="7" t="s">
+        <v>1457</v>
+      </c>
+      <c r="L1446" s="7">
+        <v>1036</v>
+      </c>
+      <c r="T1446" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1447" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1447" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1447" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J1447" s="1">
+        <v>46233</v>
+      </c>
+      <c r="K1447" s="7" t="s">
+        <v>1458</v>
+      </c>
+      <c r="L1447" s="7">
+        <v>1098</v>
+      </c>
+      <c r="T1447" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1448" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1448" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1448" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="I1448" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="J1448" s="1">
+        <v>46234</v>
+      </c>
+      <c r="K1448" s="7" t="s">
+        <v>1460</v>
+      </c>
+      <c r="L1448" s="7">
+        <v>567</v>
+      </c>
+      <c r="M1448" s="7">
+        <v>51</v>
+      </c>
+      <c r="N1448" s="7">
+        <v>4.47</v>
+      </c>
+      <c r="P1448" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1449" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1449" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1449" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1449" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="J1449" s="1">
+        <v>46235</v>
+      </c>
+      <c r="K1449" s="7" t="s">
+        <v>1461</v>
+      </c>
+      <c r="L1449" s="7">
+        <v>71</v>
+      </c>
+      <c r="M1449" s="7">
+        <v>738</v>
+      </c>
+      <c r="N1449" s="7">
+        <v>7.21</v>
+      </c>
+      <c r="P1449" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="T1449" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1450" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1450" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1450" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1450" s="9" t="s">
+        <v>1463</v>
+      </c>
+      <c r="I1450" s="9" t="s">
+        <v>1462</v>
+      </c>
+      <c r="J1450" s="1">
+        <v>46237</v>
+      </c>
+      <c r="K1450" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="L1450" s="7">
+        <v>438</v>
+      </c>
+      <c r="M1450" s="7">
+        <v>79</v>
+      </c>
+      <c r="N1450" s="7">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="P1450" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1451" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1451" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1451" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1451" s="9" t="s">
+        <v>1463</v>
+      </c>
+      <c r="I1451" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1451" s="1">
+        <v>46238</v>
+      </c>
+      <c r="P1451" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="T1451" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1452" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1452" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1452" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1452" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="I1452" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="J1452" s="1">
+        <v>46239</v>
+      </c>
+      <c r="K1452" s="7" t="s">
+        <v>1465</v>
+      </c>
+      <c r="L1452" s="7">
+        <v>462</v>
+      </c>
+      <c r="M1452" s="7">
+        <v>20</v>
+      </c>
+      <c r="N1452" s="7">
+        <v>4.46</v>
+      </c>
+      <c r="P1452" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="T1452" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1453" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1453" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1453" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1453" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="J1453" s="1">
+        <v>46240</v>
+      </c>
+      <c r="K1453" s="7" t="s">
+        <v>1467</v>
+      </c>
+      <c r="P1453" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="T1453" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1454" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1454" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1454" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="I1454" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="J1454" s="1">
+        <v>46240</v>
+      </c>
+      <c r="K1454" s="7" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L1454" s="7">
+        <v>446</v>
+      </c>
+      <c r="M1454" s="7">
+        <v>0</v>
+      </c>
+      <c r="N1454" s="7">
+        <v>3.38</v>
+      </c>
+      <c r="P1454" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="T1454" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1455" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1455" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1455" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1455" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="J1455" s="1">
+        <v>46242</v>
+      </c>
+      <c r="K1455" s="7" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1456" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1456" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1456" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1456" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="J1456" s="1">
+        <v>46242</v>
+      </c>
+      <c r="K1456" s="7" t="s">
+        <v>517</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y1445" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Bike"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1430">
     <sortCondition ref="J2:J1430"/>
     <sortCondition ref="K2:K1430"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E40D38F-49DD-410A-BB6A-774F12CA76C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12122ECF-6B87-4DAF-B34F-59C9D818EB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8325" uniqueCount="1472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8345" uniqueCount="1475">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4452,6 +4452,15 @@
   </si>
   <si>
     <t>00:48:27.7</t>
+  </si>
+  <si>
+    <t>00:29:35.3</t>
+  </si>
+  <si>
+    <t>00:57:35.1</t>
+  </si>
+  <si>
+    <t>00:59:45.1</t>
   </si>
 </sst>
 </file>
@@ -4987,7 +4996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1459"/>
+  <dimension ref="A1:Y1462"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -41513,6 +41522,90 @@
         <v>1471</v>
       </c>
     </row>
+    <row r="1460" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1460" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1460" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1460" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1460" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="J1460" s="1">
+        <v>46245</v>
+      </c>
+      <c r="K1460" s="7" t="s">
+        <v>1472</v>
+      </c>
+      <c r="P1460" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1461" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1461" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1461" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1461" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1461" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="J1461" s="1">
+        <v>46245</v>
+      </c>
+      <c r="K1461" s="7" t="s">
+        <v>1473</v>
+      </c>
+      <c r="P1461" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1462" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1462" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1462" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1462" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1462" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="J1462" s="1">
+        <v>46245</v>
+      </c>
+      <c r="K1462" s="7" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L1462" s="7">
+        <v>814</v>
+      </c>
+      <c r="M1462" s="7">
+        <v>7</v>
+      </c>
+      <c r="N1462" s="7">
+        <v>5.79</v>
+      </c>
+      <c r="P1462" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1430">
     <sortCondition ref="J2:J1430"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12122ECF-6B87-4DAF-B34F-59C9D818EB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EE0E3F-C69B-4E03-9DD7-FA9A777C2380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8345" uniqueCount="1475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8369" uniqueCount="1479">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4461,6 +4461,18 @@
   </si>
   <si>
     <t>00:59:45.1</t>
+  </si>
+  <si>
+    <t>00:33:34.4</t>
+  </si>
+  <si>
+    <t>01:07:08.9</t>
+  </si>
+  <si>
+    <t>01:28:01.7</t>
+  </si>
+  <si>
+    <t>Paradieslikurve</t>
   </si>
 </sst>
 </file>
@@ -4996,7 +5008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1462"/>
+  <dimension ref="A1:Y1466"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -41606,6 +41618,120 @@
         <v>1051</v>
       </c>
     </row>
+    <row r="1463" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1463" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1463" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1463" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1463" s="9" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E1463" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="I1463" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="J1463" s="1">
+        <v>46247</v>
+      </c>
+      <c r="L1463" s="7">
+        <v>320</v>
+      </c>
+      <c r="M1463" s="7">
+        <v>313</v>
+      </c>
+      <c r="N1463" s="7">
+        <v>6.35</v>
+      </c>
+      <c r="P1463" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1464" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1464" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1464" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1464" s="2"/>
+      <c r="E1464" s="2"/>
+      <c r="F1464" s="2"/>
+      <c r="G1464" s="2"/>
+      <c r="H1464" s="2"/>
+      <c r="I1464" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1464" s="1">
+        <v>46248</v>
+      </c>
+      <c r="K1464" s="7" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1465" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1465" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1465" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1465" s="2"/>
+      <c r="E1465" s="2"/>
+      <c r="F1465" s="2"/>
+      <c r="G1465" s="2"/>
+      <c r="H1465" s="2"/>
+      <c r="I1465" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="J1465" s="1">
+        <v>46248</v>
+      </c>
+      <c r="K1465" s="7" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1466" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1466" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1466" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1466" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E1466" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F1466" s="2"/>
+      <c r="G1466" s="2"/>
+      <c r="H1466" s="2"/>
+      <c r="I1466" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J1466" s="1">
+        <v>46248</v>
+      </c>
+      <c r="K1466" s="7" t="s">
+        <v>1477</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1430">
     <sortCondition ref="J2:J1430"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94FD78A-DA3C-4845-9010-F3CEC0125409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BD83C6-9A38-4CC6-A2D1-3743A74C4EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8410" uniqueCount="1485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8447" uniqueCount="1492">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4491,6 +4491,27 @@
   </si>
   <si>
     <t>01:19:30.3</t>
+  </si>
+  <si>
+    <t>00:30:37.0</t>
+  </si>
+  <si>
+    <t>00:57:56.1</t>
+  </si>
+  <si>
+    <t>00:28:08.9</t>
+  </si>
+  <si>
+    <t>00:33:04.7</t>
+  </si>
+  <si>
+    <t>00:38:01.1</t>
+  </si>
+  <si>
+    <t>00:55:24.4</t>
+  </si>
+  <si>
+    <t>01:02:35.0</t>
   </si>
 </sst>
 </file>
@@ -5026,7 +5047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1473"/>
+  <dimension ref="A1:Y1480"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -41909,7 +41930,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="1473" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1473" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1473" s="7" t="s">
         <v>51</v>
       </c>
@@ -41938,6 +41959,181 @@
         <v>9.48</v>
       </c>
       <c r="P1473" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1474" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1474" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1474" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1474" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="J1474" s="1">
+        <v>46257</v>
+      </c>
+      <c r="K1474" s="7" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1475" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1475" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1475" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1475" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="J1475" s="1">
+        <v>46257</v>
+      </c>
+      <c r="K1475" s="7" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1476" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1476" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1476" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J1476" s="1">
+        <v>46259</v>
+      </c>
+      <c r="K1476" s="7" t="s">
+        <v>1487</v>
+      </c>
+      <c r="L1476" s="7">
+        <v>1061</v>
+      </c>
+      <c r="T1476" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1477" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1477" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1477" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="J1477" s="1">
+        <v>46260</v>
+      </c>
+      <c r="K1477" s="7" t="s">
+        <v>1488</v>
+      </c>
+      <c r="L1477" s="7">
+        <v>1106</v>
+      </c>
+      <c r="T1477" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1478" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1478" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1478" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1478" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="I1478" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="J1478" s="1">
+        <v>46261</v>
+      </c>
+      <c r="K1478" s="7" t="s">
+        <v>1489</v>
+      </c>
+      <c r="L1478" s="7">
+        <v>456</v>
+      </c>
+      <c r="M1478" s="7">
+        <v>13</v>
+      </c>
+      <c r="N1478" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="P1478" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1479" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1479" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1479" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1479" s="2"/>
+      <c r="E1479" s="2"/>
+      <c r="F1479" s="2"/>
+      <c r="G1479" s="2"/>
+      <c r="H1479" s="2"/>
+      <c r="I1479" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="J1479" s="1">
+        <v>46262</v>
+      </c>
+      <c r="K1479" s="7" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1480" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1480" s="7" t="s">
+        <v>788</v>
+      </c>
+      <c r="I1480" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="J1480" s="1">
+        <v>46264</v>
+      </c>
+      <c r="K1480" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L1480" s="7">
+        <v>546</v>
+      </c>
+      <c r="M1480" s="7">
+        <v>149</v>
+      </c>
+      <c r="N1480" s="7">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="P1480" s="7" t="s">
         <v>1051</v>
       </c>
     </row>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BD83C6-9A38-4CC6-A2D1-3743A74C4EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BFC56F-42A7-4E89-9E03-A9BA2A740CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="all" sheetId="7" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Y$1469</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">all!$A$1:$Y$1480</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42062,7 +42062,7 @@
         <v>721</v>
       </c>
       <c r="I1478" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J1478" s="1">
         <v>46261</v>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C1EDB2-E947-4B71-B695-8F21124EC8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE71C90-CC80-462E-B7C4-2190A57232CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8486" uniqueCount="1499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8509" uniqueCount="1505">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4533,6 +4533,24 @@
   </si>
   <si>
     <t>01:24:44.0</t>
+  </si>
+  <si>
+    <t>Grimsel Hospiz</t>
+  </si>
+  <si>
+    <t>Lauteraarhuette</t>
+  </si>
+  <si>
+    <t>01:49:23.0</t>
+  </si>
+  <si>
+    <t>03:26:48.0</t>
+  </si>
+  <si>
+    <t>00:41:18.4</t>
+  </si>
+  <si>
+    <t>01:02:46.0</t>
   </si>
 </sst>
 </file>
@@ -5068,7 +5086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1485"/>
+  <dimension ref="A1:Y1489"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -42330,6 +42348,116 @@
         <v>1497</v>
       </c>
     </row>
+    <row r="1486" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1486" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1486" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1486" s="9" t="s">
+        <v>1499</v>
+      </c>
+      <c r="I1486" s="9" t="s">
+        <v>1500</v>
+      </c>
+      <c r="J1486" s="1">
+        <v>46270</v>
+      </c>
+      <c r="K1486" s="7" t="s">
+        <v>1501</v>
+      </c>
+      <c r="L1486" s="7">
+        <v>719</v>
+      </c>
+      <c r="M1486" s="7">
+        <v>294</v>
+      </c>
+      <c r="N1486" s="7">
+        <v>10.52</v>
+      </c>
+      <c r="P1486" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1487" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1487" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1487" s="9" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D1487" s="9" t="s">
+        <v>1500</v>
+      </c>
+      <c r="I1487" s="9" t="s">
+        <v>1499</v>
+      </c>
+      <c r="J1487" s="1">
+        <v>46270</v>
+      </c>
+      <c r="K1487" s="7" t="s">
+        <v>1502</v>
+      </c>
+      <c r="L1487" s="7">
+        <v>1000</v>
+      </c>
+      <c r="M1487" s="7">
+        <v>1002</v>
+      </c>
+      <c r="N1487" s="7">
+        <v>20.96</v>
+      </c>
+      <c r="P1487" s="7" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1488" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1488" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C1488" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J1488" s="1">
+        <v>46271</v>
+      </c>
+      <c r="K1488" s="7" t="s">
+        <v>1503</v>
+      </c>
+      <c r="L1488" s="7">
+        <v>1307</v>
+      </c>
+      <c r="T1488" s="7" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1489" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1489" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1489" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1489" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1489" s="1">
+        <v>46273</v>
+      </c>
+      <c r="K1489" s="7" t="s">
+        <v>1504</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1433">
     <sortCondition ref="J2:J1433"/>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE71C90-CC80-462E-B7C4-2190A57232CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B922E6E-6C58-430A-849E-32878526A2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8509" uniqueCount="1505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8515" uniqueCount="1506">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4551,6 +4551,9 @@
   </si>
   <si>
     <t>01:02:46.0</t>
+  </si>
+  <si>
+    <t>00:57:22.3</t>
   </si>
 </sst>
 </file>
@@ -5086,7 +5089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1489"/>
+  <dimension ref="A1:Y1490"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -42438,7 +42441,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="1489" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1489" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1489" s="7" t="s">
         <v>55</v>
       </c>
@@ -42456,6 +42459,38 @@
       </c>
       <c r="K1489" s="7" t="s">
         <v>1504</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1490" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1490" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1490" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="I1490" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="J1490" s="1">
+        <v>46275</v>
+      </c>
+      <c r="K1490" s="7" t="s">
+        <v>1505</v>
+      </c>
+      <c r="L1490" s="7">
+        <v>552</v>
+      </c>
+      <c r="M1490" s="7">
+        <v>146</v>
+      </c>
+      <c r="N1490" s="7">
+        <v>7.37</v>
+      </c>
+      <c r="P1490" s="7" t="s">
+        <v>1051</v>
       </c>
     </row>
   </sheetData>

--- a/data/touren.xlsx
+++ b/data/touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B922E6E-6C58-430A-849E-32878526A2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4454D74-D4E8-4612-9D6D-D9092934C9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="772" xr2:uid="{8EFC6F8A-1858-4E8D-AE4F-2D7EE50AAC04}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8515" uniqueCount="1506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8526" uniqueCount="1508">
   <si>
     <t>Niesen Plattform</t>
   </si>
@@ -4554,6 +4554,12 @@
   </si>
   <si>
     <t>00:57:22.3</t>
+  </si>
+  <si>
+    <t>00:32:36.9</t>
+  </si>
+  <si>
+    <t>00:49:54.8</t>
   </si>
 </sst>
 </file>
@@ -5089,7 +5095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D437FB2D-34B2-4A5D-9E9C-C2A0B074F473}">
-  <dimension ref="A1:Y1490"/>
+  <dimension ref="A1:Y1492"/>
   <sheetFormatPr defaultColWidth="204" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.54296875" style="7" customWidth="1"/>
@@ -42493,6 +42499,58 @@
         <v>1051</v>
       </c>
     </row>
+    <row r="1491" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1491" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1491" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1491" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1491" s="2"/>
+      <c r="E1491" s="2"/>
+      <c r="F1491" s="2"/>
+      <c r="G1491" s="2"/>
+      <c r="H1491" s="2"/>
+      <c r="I1491" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1491" s="1">
+        <v>46276</v>
+      </c>
+      <c r="K1491" s="7" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1492" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1492" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1492" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1492" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E1492" s="2"/>
+      <c r="F1492" s="2"/>
+      <c r="G1492" s="2"/>
+      <c r="H1492" s="2"/>
+      <c r="I1492" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="J1492" s="1">
+        <v>46276</v>
+      </c>
+      <c r="K1492" s="7" t="s">
+        <v>1507</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y1433">
     <sortCondition ref="J2:J1433"/>
